--- a/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
+++ b/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Listed company</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -1231,11 +1231,7 @@
       <c r="M11" s="12" t="n"/>
       <c r="N11" s="12" t="n"/>
       <c r="O11" s="12" t="n"/>
-      <c r="P11" s="12" t="inlineStr">
-        <is>
-          <t>EstimatedMarketCapitalizationInEUR</t>
-        </is>
-      </c>
+      <c r="P11" s="12" t="n"/>
       <c r="Q11" s="12" t="n"/>
       <c r="R11" s="12" t="n"/>
     </row>
@@ -1293,11 +1289,7 @@
       <c r="M12" s="12" t="n"/>
       <c r="N12" s="12" t="n"/>
       <c r="O12" s="12" t="n"/>
-      <c r="P12" s="12" t="inlineStr">
-        <is>
-          <t>EstimatedMinoritiesInterestInEUR</t>
-        </is>
-      </c>
+      <c r="P12" s="12" t="n"/>
       <c r="Q12" s="12" t="n"/>
       <c r="R12" s="12" t="n"/>
     </row>
@@ -1410,11 +1402,7 @@
       <c r="M14" s="12" t="n"/>
       <c r="N14" s="12" t="n"/>
       <c r="O14" s="12" t="n"/>
-      <c r="P14" s="12" t="inlineStr">
-        <is>
-          <t>EstimatedTotalEquityAndDebtInEUR</t>
-        </is>
-      </c>
+      <c r="P14" s="12" t="n"/>
       <c r="Q14" s="12" t="n"/>
       <c r="R14" s="12" t="n"/>
     </row>

--- a/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
+++ b/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d93912\IdeaProjects\Dataland\dataland-framework-toolbox\inputs\sfdr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDDF7F7-2707-4710-B87B-DE2E1C34A602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81786C1F-2A5F-471C-8D4E-E5E710325A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="388">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -1303,6 +1303,9 @@
   </si>
   <si>
     <t>A country’s total economic output in euros. See also Regulation (EU) 2022/1288, Annex I, formula (4). Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 15</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -1410,7 +1413,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1464,7 +1467,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
@@ -1853,7 +1855,7 @@
       </c>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="23">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -1887,13 +1889,13 @@
       <c r="N2" s="6"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="23">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="23" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -2058,10 +2060,18 @@
         <v>385</v>
       </c>
       <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
+      <c r="H7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
@@ -2345,7 +2355,7 @@
       <c r="R14" s="12"/>
     </row>
     <row r="15" spans="1:18" s="6" customFormat="1">
-      <c r="A15" s="23">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -2378,7 +2388,7 @@
       </c>
     </row>
     <row r="16" spans="1:18" s="6" customFormat="1">
-      <c r="A16" s="23">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -2409,7 +2419,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" s="6" customFormat="1">
-      <c r="A17" s="23">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -2442,7 +2452,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" s="6" customFormat="1">
-      <c r="A18" s="23">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -2475,7 +2485,7 @@
       </c>
     </row>
     <row r="19" spans="1:11" s="6" customFormat="1">
-      <c r="A19" s="23">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -2506,7 +2516,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" s="6" customFormat="1">
-      <c r="A20" s="23">
+      <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -2537,7 +2547,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" s="6" customFormat="1">
-      <c r="A21" s="23">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -2568,7 +2578,7 @@
       </c>
     </row>
     <row r="22" spans="1:11" s="6" customFormat="1">
-      <c r="A22" s="23">
+      <c r="A22" s="4">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -2601,7 +2611,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" s="6" customFormat="1">
-      <c r="A23" s="23">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -2632,7 +2642,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" s="6" customFormat="1">
-      <c r="A24" s="23">
+      <c r="A24" s="4">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -2663,7 +2673,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" s="6" customFormat="1">
-      <c r="A25" s="23">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -2694,7 +2704,7 @@
       </c>
     </row>
     <row r="26" spans="1:11" s="6" customFormat="1">
-      <c r="A26" s="23">
+      <c r="A26" s="4">
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -2725,7 +2735,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" s="6" customFormat="1">
-      <c r="A27" s="23">
+      <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -2756,7 +2766,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" s="6" customFormat="1">
-      <c r="A28" s="23">
+      <c r="A28" s="4">
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -2787,7 +2797,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" s="6" customFormat="1">
-      <c r="A29" s="23">
+      <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -2818,7 +2828,7 @@
       </c>
     </row>
     <row r="30" spans="1:11" s="6" customFormat="1">
-      <c r="A30" s="23">
+      <c r="A30" s="4">
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -2849,7 +2859,7 @@
       </c>
     </row>
     <row r="31" spans="1:11" s="6" customFormat="1">
-      <c r="A31" s="23">
+      <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -2880,7 +2890,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" s="6" customFormat="1">
-      <c r="A32" s="23">
+      <c r="A32" s="4">
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -2911,7 +2921,7 @@
       </c>
     </row>
     <row r="33" spans="1:11" s="6" customFormat="1">
-      <c r="A33" s="23">
+      <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -2941,7 +2951,7 @@
       </c>
     </row>
     <row r="34" spans="1:11" s="6" customFormat="1">
-      <c r="A34" s="23">
+      <c r="A34" s="4">
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
@@ -2972,7 +2982,7 @@
       </c>
     </row>
     <row r="35" spans="1:11" s="6" customFormat="1">
-      <c r="A35" s="23">
+      <c r="A35" s="4">
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
@@ -3003,7 +3013,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" s="6" customFormat="1">
-      <c r="A36" s="23">
+      <c r="A36" s="4">
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -3036,7 +3046,7 @@
       </c>
     </row>
     <row r="37" spans="1:11" s="6" customFormat="1">
-      <c r="A37" s="23">
+      <c r="A37" s="4">
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -3069,7 +3079,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" s="6" customFormat="1">
-      <c r="A38" s="23">
+      <c r="A38" s="4">
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -3102,7 +3112,7 @@
       </c>
     </row>
     <row r="39" spans="1:11" s="6" customFormat="1">
-      <c r="A39" s="23">
+      <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -3135,7 +3145,7 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="6" customFormat="1">
-      <c r="A40" s="23">
+      <c r="A40" s="4">
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -3168,7 +3178,7 @@
       </c>
     </row>
     <row r="41" spans="1:11" s="6" customFormat="1">
-      <c r="A41" s="23">
+      <c r="A41" s="4">
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -3201,7 +3211,7 @@
       </c>
     </row>
     <row r="42" spans="1:11" s="6" customFormat="1">
-      <c r="A42" s="23">
+      <c r="A42" s="4">
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -3234,7 +3244,7 @@
       </c>
     </row>
     <row r="43" spans="1:11" s="6" customFormat="1">
-      <c r="A43" s="23">
+      <c r="A43" s="4">
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -3267,7 +3277,7 @@
       </c>
     </row>
     <row r="44" spans="1:11" s="6" customFormat="1">
-      <c r="A44" s="23">
+      <c r="A44" s="4">
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -3300,7 +3310,7 @@
       </c>
     </row>
     <row r="45" spans="1:11" s="6" customFormat="1">
-      <c r="A45" s="23">
+      <c r="A45" s="4">
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -3333,7 +3343,7 @@
       </c>
     </row>
     <row r="46" spans="1:11" s="6" customFormat="1">
-      <c r="A46" s="23">
+      <c r="A46" s="4">
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -3366,7 +3376,7 @@
       </c>
     </row>
     <row r="47" spans="1:11" s="6" customFormat="1">
-      <c r="A47" s="23">
+      <c r="A47" s="4">
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -3399,7 +3409,7 @@
       </c>
     </row>
     <row r="48" spans="1:11" s="6" customFormat="1">
-      <c r="A48" s="23">
+      <c r="A48" s="4">
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -3432,7 +3442,7 @@
       </c>
     </row>
     <row r="49" spans="1:11" s="6" customFormat="1">
-      <c r="A49" s="23">
+      <c r="A49" s="4">
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -3465,7 +3475,7 @@
       </c>
     </row>
     <row r="50" spans="1:11" s="6" customFormat="1">
-      <c r="A50" s="23">
+      <c r="A50" s="4">
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -3497,7 +3507,7 @@
       </c>
     </row>
     <row r="51" spans="1:11" s="6" customFormat="1">
-      <c r="A51" s="23">
+      <c r="A51" s="4">
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
@@ -3529,7 +3539,7 @@
       </c>
     </row>
     <row r="52" spans="1:11" s="6" customFormat="1">
-      <c r="A52" s="23">
+      <c r="A52" s="4">
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -3562,7 +3572,7 @@
       </c>
     </row>
     <row r="53" spans="1:11" s="6" customFormat="1">
-      <c r="A53" s="23">
+      <c r="A53" s="4">
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
@@ -3594,7 +3604,7 @@
       </c>
     </row>
     <row r="54" spans="1:11" s="6" customFormat="1">
-      <c r="A54" s="23">
+      <c r="A54" s="4">
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
@@ -3626,7 +3636,7 @@
       </c>
     </row>
     <row r="55" spans="1:11" s="6" customFormat="1">
-      <c r="A55" s="23">
+      <c r="A55" s="4">
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
@@ -3658,7 +3668,7 @@
       </c>
     </row>
     <row r="56" spans="1:11" s="6" customFormat="1">
-      <c r="A56" s="23">
+      <c r="A56" s="4">
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
@@ -3690,7 +3700,7 @@
       </c>
     </row>
     <row r="57" spans="1:11" s="6" customFormat="1">
-      <c r="A57" s="23">
+      <c r="A57" s="4">
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
@@ -3722,7 +3732,7 @@
       </c>
     </row>
     <row r="58" spans="1:11" s="6" customFormat="1">
-      <c r="A58" s="23">
+      <c r="A58" s="4">
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
@@ -3754,7 +3764,7 @@
       </c>
     </row>
     <row r="59" spans="1:11" s="6" customFormat="1">
-      <c r="A59" s="23">
+      <c r="A59" s="4">
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
@@ -3786,7 +3796,7 @@
       </c>
     </row>
     <row r="60" spans="1:11" s="6" customFormat="1">
-      <c r="A60" s="23">
+      <c r="A60" s="4">
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
@@ -3819,7 +3829,7 @@
       </c>
     </row>
     <row r="61" spans="1:11" s="6" customFormat="1">
-      <c r="A61" s="23">
+      <c r="A61" s="4">
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
@@ -3852,7 +3862,7 @@
       </c>
     </row>
     <row r="62" spans="1:11" s="6" customFormat="1">
-      <c r="A62" s="23">
+      <c r="A62" s="4">
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
@@ -3885,7 +3895,7 @@
       </c>
     </row>
     <row r="63" spans="1:11" s="6" customFormat="1">
-      <c r="A63" s="23">
+      <c r="A63" s="4">
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
@@ -3918,7 +3928,7 @@
       </c>
     </row>
     <row r="64" spans="1:11" s="6" customFormat="1">
-      <c r="A64" s="23">
+      <c r="A64" s="4">
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
@@ -3950,7 +3960,7 @@
       </c>
     </row>
     <row r="65" spans="1:11" s="6" customFormat="1">
-      <c r="A65" s="23">
+      <c r="A65" s="4">
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
@@ -3982,7 +3992,7 @@
       </c>
     </row>
     <row r="66" spans="1:11" s="6" customFormat="1">
-      <c r="A66" s="23">
+      <c r="A66" s="4">
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
@@ -4015,7 +4025,7 @@
       </c>
     </row>
     <row r="67" spans="1:11" s="6" customFormat="1">
-      <c r="A67" s="23">
+      <c r="A67" s="4">
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
@@ -4048,7 +4058,7 @@
       </c>
     </row>
     <row r="68" spans="1:11" s="6" customFormat="1">
-      <c r="A68" s="23">
+      <c r="A68" s="4">
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
@@ -4081,7 +4091,7 @@
       </c>
     </row>
     <row r="69" spans="1:11" s="6" customFormat="1">
-      <c r="A69" s="23">
+      <c r="A69" s="4">
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
@@ -4114,7 +4124,7 @@
       </c>
     </row>
     <row r="70" spans="1:11" s="6" customFormat="1">
-      <c r="A70" s="23">
+      <c r="A70" s="4">
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
@@ -4147,7 +4157,7 @@
       </c>
     </row>
     <row r="71" spans="1:11" s="6" customFormat="1">
-      <c r="A71" s="23">
+      <c r="A71" s="4">
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
@@ -4179,7 +4189,7 @@
       </c>
     </row>
     <row r="72" spans="1:11" s="6" customFormat="1">
-      <c r="A72" s="23">
+      <c r="A72" s="4">
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
@@ -4211,7 +4221,7 @@
       </c>
     </row>
     <row r="73" spans="1:11" s="6" customFormat="1">
-      <c r="A73" s="23">
+      <c r="A73" s="4">
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
@@ -4243,7 +4253,7 @@
       </c>
     </row>
     <row r="74" spans="1:11" s="6" customFormat="1">
-      <c r="A74" s="23">
+      <c r="A74" s="4">
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
@@ -4275,7 +4285,7 @@
       </c>
     </row>
     <row r="75" spans="1:11" s="6" customFormat="1">
-      <c r="A75" s="23">
+      <c r="A75" s="4">
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
@@ -4307,7 +4317,7 @@
       </c>
     </row>
     <row r="76" spans="1:11" s="6" customFormat="1">
-      <c r="A76" s="23">
+      <c r="A76" s="4">
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
@@ -4340,7 +4350,7 @@
       </c>
     </row>
     <row r="77" spans="1:11" s="6" customFormat="1">
-      <c r="A77" s="23">
+      <c r="A77" s="4">
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
@@ -4373,7 +4383,7 @@
       </c>
     </row>
     <row r="78" spans="1:11" s="6" customFormat="1">
-      <c r="A78" s="23">
+      <c r="A78" s="4">
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
@@ -4406,7 +4416,7 @@
       </c>
     </row>
     <row r="79" spans="1:11" s="6" customFormat="1">
-      <c r="A79" s="23">
+      <c r="A79" s="4">
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
@@ -4439,7 +4449,7 @@
       </c>
     </row>
     <row r="80" spans="1:11" s="6" customFormat="1">
-      <c r="A80" s="23">
+      <c r="A80" s="4">
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
@@ -4471,7 +4481,7 @@
       </c>
     </row>
     <row r="81" spans="1:11" s="6" customFormat="1">
-      <c r="A81" s="23">
+      <c r="A81" s="4">
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
@@ -4504,7 +4514,7 @@
       </c>
     </row>
     <row r="82" spans="1:11" s="6" customFormat="1">
-      <c r="A82" s="23">
+      <c r="A82" s="4">
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
@@ -4537,7 +4547,7 @@
       </c>
     </row>
     <row r="83" spans="1:11" s="6" customFormat="1">
-      <c r="A83" s="23">
+      <c r="A83" s="4">
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
@@ -4570,7 +4580,7 @@
       </c>
     </row>
     <row r="84" spans="1:11" s="6" customFormat="1">
-      <c r="A84" s="23">
+      <c r="A84" s="4">
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
@@ -4602,7 +4612,7 @@
       </c>
     </row>
     <row r="85" spans="1:11" s="6" customFormat="1">
-      <c r="A85" s="23">
+      <c r="A85" s="4">
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
@@ -4634,7 +4644,7 @@
       </c>
     </row>
     <row r="86" spans="1:11" s="6" customFormat="1">
-      <c r="A86" s="23">
+      <c r="A86" s="4">
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
@@ -4665,7 +4675,7 @@
       </c>
     </row>
     <row r="87" spans="1:11" s="6" customFormat="1">
-      <c r="A87" s="23">
+      <c r="A87" s="4">
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
@@ -4696,7 +4706,7 @@
       </c>
     </row>
     <row r="88" spans="1:11" s="6" customFormat="1">
-      <c r="A88" s="23">
+      <c r="A88" s="4">
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
@@ -4727,7 +4737,7 @@
       </c>
     </row>
     <row r="89" spans="1:11" s="6" customFormat="1">
-      <c r="A89" s="23">
+      <c r="A89" s="4">
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
@@ -4758,7 +4768,7 @@
       </c>
     </row>
     <row r="90" spans="1:11" s="6" customFormat="1">
-      <c r="A90" s="23">
+      <c r="A90" s="4">
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
@@ -4789,7 +4799,7 @@
       </c>
     </row>
     <row r="91" spans="1:11" s="6" customFormat="1">
-      <c r="A91" s="23">
+      <c r="A91" s="4">
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
@@ -4822,7 +4832,7 @@
       </c>
     </row>
     <row r="92" spans="1:11" s="6" customFormat="1">
-      <c r="A92" s="23">
+      <c r="A92" s="4">
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
@@ -4855,7 +4865,7 @@
       </c>
     </row>
     <row r="93" spans="1:11" s="6" customFormat="1">
-      <c r="A93" s="23">
+      <c r="A93" s="4">
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
@@ -4887,7 +4897,7 @@
       </c>
     </row>
     <row r="94" spans="1:11" s="6" customFormat="1">
-      <c r="A94" s="23">
+      <c r="A94" s="4">
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
@@ -4919,7 +4929,7 @@
       </c>
     </row>
     <row r="95" spans="1:11" s="6" customFormat="1">
-      <c r="A95" s="23">
+      <c r="A95" s="4">
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
@@ -4950,7 +4960,7 @@
       </c>
     </row>
     <row r="96" spans="1:11" s="6" customFormat="1">
-      <c r="A96" s="23">
+      <c r="A96" s="4">
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
@@ -4983,7 +4993,7 @@
       </c>
     </row>
     <row r="97" spans="1:15" s="6" customFormat="1">
-      <c r="A97" s="23">
+      <c r="A97" s="4">
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
@@ -5015,7 +5025,7 @@
       </c>
     </row>
     <row r="98" spans="1:15" s="6" customFormat="1">
-      <c r="A98" s="23">
+      <c r="A98" s="4">
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
@@ -5047,7 +5057,7 @@
       </c>
     </row>
     <row r="99" spans="1:15" s="6" customFormat="1">
-      <c r="A99" s="23">
+      <c r="A99" s="4">
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
@@ -5079,7 +5089,7 @@
       </c>
     </row>
     <row r="100" spans="1:15" s="6" customFormat="1">
-      <c r="A100" s="23">
+      <c r="A100" s="4">
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
@@ -5112,7 +5122,7 @@
       </c>
     </row>
     <row r="101" spans="1:15" s="6" customFormat="1">
-      <c r="A101" s="23">
+      <c r="A101" s="4">
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
@@ -5145,7 +5155,7 @@
       </c>
     </row>
     <row r="102" spans="1:15" s="6" customFormat="1">
-      <c r="A102" s="23">
+      <c r="A102" s="4">
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
@@ -5176,7 +5186,7 @@
       </c>
     </row>
     <row r="103" spans="1:15" s="6" customFormat="1">
-      <c r="A103" s="23">
+      <c r="A103" s="4">
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
@@ -5208,7 +5218,7 @@
       </c>
     </row>
     <row r="104" spans="1:15" s="6" customFormat="1">
-      <c r="A104" s="23">
+      <c r="A104" s="4">
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
@@ -5240,7 +5250,7 @@
       </c>
     </row>
     <row r="105" spans="1:15" s="6" customFormat="1">
-      <c r="A105" s="23">
+      <c r="A105" s="4">
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
@@ -5272,7 +5282,7 @@
       </c>
     </row>
     <row r="106" spans="1:15" s="6" customFormat="1">
-      <c r="A106" s="23">
+      <c r="A106" s="4">
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
@@ -5304,7 +5314,7 @@
       </c>
     </row>
     <row r="107" spans="1:15" s="6" customFormat="1">
-      <c r="A107" s="23">
+      <c r="A107" s="4">
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
@@ -5336,7 +5346,7 @@
       </c>
     </row>
     <row r="108" spans="1:15">
-      <c r="A108" s="23">
+      <c r="A108" s="4">
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
@@ -5369,7 +5379,7 @@
       </c>
     </row>
     <row r="109" spans="1:15">
-      <c r="A109" s="23">
+      <c r="A109" s="4">
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
@@ -5402,7 +5412,7 @@
       </c>
     </row>
     <row r="110" spans="1:15">
-      <c r="A110" s="23">
+      <c r="A110" s="4">
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
@@ -5439,7 +5449,7 @@
       <c r="O110" s="6"/>
     </row>
     <row r="111" spans="1:15">
-      <c r="A111" s="23">
+      <c r="A111" s="4">
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">

--- a/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
+++ b/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\srv\data\dataland\dataland-framework-toolbox\inputs\sfdr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d93912\IdeaProjects\Dataland\dataland-framework-toolbox\inputs\sfdr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815CF9E9-3A7D-494B-AD1A-2F6BDD17ABFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81786C1F-2A5F-471C-8D4E-E5E710325A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Framework Data Model" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Framework Data Model'!$A$1:$N$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Framework Data Model'!$A$1:$N$109</definedName>
     <definedName name="IQ_CH">110000</definedName>
     <definedName name="IQ_CQ">5000</definedName>
     <definedName name="IQ_CY">10000</definedName>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="388">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -100,42 +100,39 @@
     <t>Field Calculation</t>
   </si>
   <si>
+    <t>Data Point Type Name Overwrite</t>
+  </si>
+  <si>
     <t>General</t>
   </si>
   <si>
-    <t>Data Date</t>
-  </si>
-  <si>
-    <t>DATA_DATE</t>
-  </si>
-  <si>
-    <t>The year for which the data is reported.</t>
-  </si>
-  <si>
     <t> </t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>Fiscal Year Deviation</t>
-  </si>
-  <si>
-    <t>FISCAL_YEAR_DEVIATION</t>
-  </si>
-  <si>
-    <t>Does the fiscal year deviate from the calendar year?</t>
-  </si>
-  <si>
     <t>Single-Select Radio Button</t>
   </si>
   <si>
-    <t>Deviation| No Deviation</t>
-  </si>
-  <si>
     <t>Extended</t>
   </si>
   <si>
+    <t>Referenced Reports</t>
+  </si>
+  <si>
+    <t>REFERENCED_REPORTS</t>
+  </si>
+  <si>
+    <t>Please upload all relevant reports for this dataset in the PDF format.</t>
+  </si>
+  <si>
+    <t>Report Preupload</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
     <t>Fiscal Year End</t>
   </si>
   <si>
@@ -145,16 +142,120 @@
     <t>The date the fiscal year ends.</t>
   </si>
   <si>
-    <t>Referenced Reports</t>
-  </si>
-  <si>
-    <t>REFERENCED_REPORTS</t>
-  </si>
-  <si>
-    <t>Please upload all relevant reports for this dataset in the PDF format.</t>
-  </si>
-  <si>
-    <t>Report Preupload</t>
+    <t>Main PCAF sector</t>
+  </si>
+  <si>
+    <t>MAIN_PCAF_SECTOR</t>
+  </si>
+  <si>
+    <t>One of the following sectors the company is mainly operating in: "Communication Services"; "Consumer Discretionary"; "Consumer Staples"; "Energy"; "Financials"; "Health Care"; "Industrials"; "Industry"; "Information Technology"; "Materials"; "Real estate"; "Sovereign"; "Utilities";</t>
+  </si>
+  <si>
+    <t>Single-Select Dropdown</t>
+  </si>
+  <si>
+    <t>Communication Services|Consumer Discretionary|Consumer Staples|Energy|Financials|Health Care|Industrials|Industry|Information Technology|Materials|Real Estate|Sovereign|Utilities</t>
+  </si>
+  <si>
+    <t>Company exchange status</t>
+  </si>
+  <si>
+    <t>COMPANY_EXCHANGE_STATUS</t>
+  </si>
+  <si>
+    <t>"Listed" if the company is listed on an exchange - otherwise "Unlisted"</t>
+  </si>
+  <si>
+    <t>Listed | Unlisted</t>
+  </si>
+  <si>
+    <t>Financial</t>
+  </si>
+  <si>
+    <t>Gross Domestic Product (GDP)</t>
+  </si>
+  <si>
+    <t>GDP_IN_EUR</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Allowed Range: [0, INF]</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>Total Revenue</t>
+  </si>
+  <si>
+    <t>TOTAL_REVENUE_IN_EUR</t>
+  </si>
+  <si>
+    <t>Total net or gross revenue in EUR for the financial year. i.e., income arising in the course of an entity's ordinary activities, the amounts derived from the sale of products and the provision of services. Overall turnover is equivalent to a firm's total revenues over some period of time. See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>Book value of debt</t>
+  </si>
+  <si>
+    <t>BOOK_VALUE_OF_DEBT_IN_EUR</t>
+  </si>
+  <si>
+    <t>Book value of debt in EUR = all debt as listed on the company balance sheet (not to be mixed up with other definitions)</t>
+  </si>
+  <si>
+    <t>Listed company</t>
+  </si>
+  <si>
+    <t>Market capitalization</t>
+  </si>
+  <si>
+    <t>MARKET_CAPITALIZATION_IN_EUR</t>
+  </si>
+  <si>
+    <t>Market capitalization in EUR calculated as: number of shares * price per share</t>
+  </si>
+  <si>
+    <t>Minorities interest</t>
+  </si>
+  <si>
+    <t>MINORITIES_INTEREST_IN_EUR</t>
+  </si>
+  <si>
+    <t>Minorities interest in EUR as potentially listed on the balance sheet for ownerships without control (typically for ownerships of less than 50%)</t>
+  </si>
+  <si>
+    <t>Enterprise Value</t>
+  </si>
+  <si>
+    <t>ENTERPRISE_VALUE_IN_EUR</t>
+  </si>
+  <si>
+    <t>The enterprise value in EUR, i.e. the sum, at fiscal year-end, of the market capitalisation of ordinary shares, the market capitalisation of preferred shares, the book value of total debt and non-controlling interests, without the deduction of cash or cash equivalents. See also Regulation (EU) 2022/1288, Annex I, top (4) and formula (1)+(2).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2</t>
+  </si>
+  <si>
+    <t>Unlisted company</t>
+  </si>
+  <si>
+    <t>Total equity and debt</t>
+  </si>
+  <si>
+    <t>TOTAL_EQUITY_AND_DEBT_IN_EUR</t>
+  </si>
+  <si>
+    <t>Sum of total equity and total debt in EUR as listed on the balance sheet</t>
+  </si>
+  <si>
+    <t>Total equity</t>
+  </si>
+  <si>
+    <t>TOTAL_EQUITY_IN_EUR</t>
+  </si>
+  <si>
+    <t>Total equity in EUR as listed on the balance sheet</t>
   </si>
   <si>
     <t>Environmental</t>
@@ -167,1448 +268,1051 @@
   </si>
   <si>
     <t>SCOPE_1_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>Allowed Range: [0, INF]</t>
-  </si>
-  <si>
-    <t>Tonnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greenhouse gas emissions </t>
-  </si>
-  <si>
-    <t>Scope 2 GHG emissions</t>
-  </si>
-  <si>
-    <t>SCOPE_2_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>Scope 2 GHG emissions (location-based)</t>
-  </si>
-  <si>
-    <t>SCOPE_2_GHG_EMISSIONS_LOCATION_IN_T</t>
-  </si>
-  <si>
-    <t>Scope 2 GHG emissions (market-based)</t>
-  </si>
-  <si>
-    <t>SCOPE_2_GHG_EMISSIONS_MARKET_IN_T</t>
-  </si>
-  <si>
-    <t>Scope 1 and 2 GHG emissions</t>
-  </si>
-  <si>
-    <t>SCOPE_1_2_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>Scope 1 and 2 GHG emissions (location-based)</t>
-  </si>
-  <si>
-    <t>SCOPE_1_2_GHG_EMISSIONS_LOCATION_IN_T</t>
-  </si>
-  <si>
-    <t>Scope 1 and 2 GHG emissions (market-based)</t>
-  </si>
-  <si>
-    <t>SCOPE_1_2_GHG_EMISSIONS_MARKET_IN_T</t>
-  </si>
-  <si>
-    <t>Scope 3 GHG emissions</t>
-  </si>
-  <si>
-    <t>SCOPE_3_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>Scope 3 upstream GHG emissions</t>
-  </si>
-  <si>
-    <t>SCOPE_3_UPSTREAM_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>SCOPE_3_DOWNSTREAM_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>Scope 1 and 2 and 3 GHG emissions</t>
-  </si>
-  <si>
-    <t>SCOPE_1_2_3_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>Scope 1 and 2 and 3 GHG emissions (location-based)</t>
-  </si>
-  <si>
-    <t>SCOPE_1_2_3_GHG_EMISSIONS_LOCATION_IN_T</t>
-  </si>
-  <si>
-    <t>Scope 1 and 2 and 3 GHG emissions (market-based)</t>
-  </si>
-  <si>
-    <t>SCOPE_1_2_3_GHG_EMISSIONS_MARKET_IN_T</t>
-  </si>
-  <si>
-    <t>Scope 4 GHG emissions</t>
-  </si>
-  <si>
-    <t>SCOPE_4_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>Scope 4, as defined by the GHG Protocol, covers emissions avoided when a product is used as a substitute for other goods or services, fulfilling the same functions but with a lower carbon intensity.</t>
-  </si>
-  <si>
-    <t>Enterprise Value</t>
-  </si>
-  <si>
-    <t>ENTERPRISE_VALUE_IN_EUR</t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>Total Revenue</t>
-  </si>
-  <si>
-    <t>TOTAL_REVENUE_IN_EUR</t>
-  </si>
-  <si>
-    <t>Carbon footprint</t>
-  </si>
-  <si>
-    <t>CARBON_FOOTPRINT_IN_T_PER_MIO_EUR_ENTERPRISE_VALUE</t>
-  </si>
-  <si>
-    <t>Tonnes / €M Enterprise Value</t>
-  </si>
-  <si>
-    <t>GHG intensity</t>
-  </si>
-  <si>
-    <t>GHG_INTENSITY_IN_T_PER_MIO_EUR_REVENUE</t>
-  </si>
-  <si>
-    <t>Tonnes / €M Revenue</t>
-  </si>
-  <si>
-    <t>GHG intensity - scope 1</t>
-  </si>
-  <si>
-    <t>GHG_INTENSITY_SCOPE_1_IN_T_PER_MIO_EUR_REVENUE</t>
-  </si>
-  <si>
-    <t>GHG intensity - scope 2</t>
-  </si>
-  <si>
-    <t>GHG_INTENSITY_SCOPE_2_IN_T_PER_MIO_EUR_REVENUE</t>
-  </si>
-  <si>
-    <t>GHG intensity - scope 3</t>
-  </si>
-  <si>
-    <t>GHG_INTENSITY_SCOPE_3_IN_T_PER_MIO_EUR_REVENUE</t>
-  </si>
-  <si>
-    <t>GHG intensity - scope 4</t>
-  </si>
-  <si>
-    <t>GHG_INTENSITY_SCOPE_4_IN_T_PER_MIO_EUR_REVENUE</t>
-  </si>
-  <si>
-    <t>Fossil Fuel Sector Exposure</t>
-  </si>
-  <si>
-    <t>FOSSIL_FUEL_SECTOR_EXPOSURE</t>
-  </si>
-  <si>
-    <t>Yes/No</t>
-  </si>
-  <si>
-    <t>Financed scope 1 and scope 2 emissions</t>
-  </si>
-  <si>
-    <t>FINANCED_SCOPE_1_2_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tonnes </t>
-  </si>
-  <si>
-    <t>Financed scope 3 emissions</t>
-  </si>
-  <si>
-    <t>FINANCED_SCOPE_3_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>Energy performance</t>
-  </si>
-  <si>
-    <t>Renewable Energy Production</t>
-  </si>
-  <si>
-    <t>RENEWABLE_ENERGY_PROD_IN_GWH</t>
-  </si>
-  <si>
-    <t>GWh</t>
-  </si>
-  <si>
-    <t>Renewable Energy Consumption</t>
-  </si>
-  <si>
-    <t>RENEWABLE_ENERGY_CONS_IN_GWH</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Production</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_PROD_IN_GWH</t>
-  </si>
-  <si>
-    <t>Relative Non-Renewable Energy Production</t>
-  </si>
-  <si>
-    <t>REL_NON_RENEWABLE_ENERGY_PROD_PCT</t>
-  </si>
-  <si>
-    <t>Percent</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_IN_GWH</t>
-  </si>
-  <si>
-    <t>Relative Non-Renewable Energy Consumption</t>
-  </si>
-  <si>
-    <t>REL_NON_RENEWABLE_ENERGY_CONS_PCT</t>
-  </si>
-  <si>
-    <t>Applicable High Impact Climate Sectors</t>
-  </si>
-  <si>
-    <t>APPLICABLE_HIGH_IMPACT_CLIMATE_SECTORS</t>
-  </si>
-  <si>
-    <t>Custom - SFDR High Impact Climate Sectors</t>
-  </si>
-  <si>
-    <t>Total High Impact Climate Sector Energy Consumption</t>
-  </si>
-  <si>
-    <t>TOTAL_HIGH_IMPACT_CLIMATE_SECTOR_ENERGY_CONS_IN_GWH</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption Fossil Fuels</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_FOSSIL_FUELS_IN_GWH</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption Crude Oil</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_CRUDE_OIL_IN_GWH</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption Natural Gas</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_NATURAL_GAS_IN_GWH</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption Lignite</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_LIGNITE_IN_GWH</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption Coal</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_COAL_IN_GWH</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption Nuclear Energy</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_NUCLEAR_ENERGY_IN_GWH</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption Other</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_OTHER_IN_GWH</t>
-  </si>
-  <si>
-    <t>Biodiversity</t>
-  </si>
-  <si>
-    <t>Primary Forest And Wooded Land Of Native Species Exposure</t>
-  </si>
-  <si>
-    <t>PRIMARY_FOREST_AND_WOODED_LAND_OF_NATIVE_SPECIES_EXPOSURE</t>
-  </si>
-  <si>
-    <t>Protected Areas Exposure</t>
-  </si>
-  <si>
-    <t>PROTECTED_AREAS_EXPOSURE</t>
-  </si>
-  <si>
-    <t>Rare Or Endangered Ecosystems Exposure</t>
-  </si>
-  <si>
-    <t>RARE_OR_ENDANGERED_ECOSYSTEMS_EXPOSURE</t>
-  </si>
-  <si>
-    <t>Highly Biodiverse Grassland Exposure</t>
-  </si>
-  <si>
-    <t>HIGHLY_BIODIVERSE_GRASSLAND_EXPOSURE</t>
-  </si>
-  <si>
-    <t>Manufacture Of Agrochemical Pesticides Products</t>
-  </si>
-  <si>
-    <t>MANUFACTURE_OF_AGROCHEMICAL_PESTICIDES_PRODUCTS</t>
-  </si>
-  <si>
-    <t>Land Degradation Desertification Soil Sealing Exposure</t>
-  </si>
-  <si>
-    <t>LAND_DEGRADATION_DESERTIFICATION_SOIL_SEALING_EXPOSURE</t>
-  </si>
-  <si>
-    <t>Sustainable Agriculture Policy</t>
-  </si>
-  <si>
-    <t>SUSTAINABLE_AGRICULTURE_POLICY</t>
-  </si>
-  <si>
-    <t>Sustainable Oceans And Seas Policy</t>
-  </si>
-  <si>
-    <t>SUSTAINABLE_OCEANS_AND_SEAS_POLICY</t>
-  </si>
-  <si>
-    <t>Threatened Species Exposure</t>
-  </si>
-  <si>
-    <t>THREATENED_SPECIES_EXPOSURE</t>
-  </si>
-  <si>
-    <t>Biodiversity Protection Policy</t>
-  </si>
-  <si>
-    <t>BIODIVERSITY_PROTECTION_POLICY</t>
-  </si>
-  <si>
-    <t>Deforestation Policy</t>
-  </si>
-  <si>
-    <t>DEFORESTATION_POLICY</t>
-  </si>
-  <si>
-    <t>Water</t>
-  </si>
-  <si>
-    <t>Emissions To Water</t>
-  </si>
-  <si>
-    <t>EMISSIONS_TO_WATER_IN_T</t>
-  </si>
-  <si>
-    <t>WATER_CONS_IN_M3</t>
-  </si>
-  <si>
-    <t>Cubic Meters</t>
-  </si>
-  <si>
-    <t>Water Reused</t>
-  </si>
-  <si>
-    <t>WATER_REUSED_IN_M3</t>
-  </si>
-  <si>
-    <t>Relative Water Usage</t>
-  </si>
-  <si>
-    <t>REL_WATER_USAGE_IN_M3_PER_MIO_EUR_REVENUE</t>
-  </si>
-  <si>
-    <t>Cubic Meters / €M Revenue</t>
-  </si>
-  <si>
-    <t>Water Management Policy</t>
-  </si>
-  <si>
-    <t>WATER_MANAGEMENT_POLICY</t>
-  </si>
-  <si>
-    <t>High Water Stress Area Exposure</t>
-  </si>
-  <si>
-    <t>HIGH_WATER_STRESS_AREA_EXPOSURE</t>
-  </si>
-  <si>
-    <t>Waste</t>
-  </si>
-  <si>
-    <t>Hazardous and Radioactive Waste</t>
-  </si>
-  <si>
-    <t>HAZARDOUS_AND_RADIOACTIVE_WASTE_IN_T</t>
-  </si>
-  <si>
-    <t>Non-Recycled Waste</t>
-  </si>
-  <si>
-    <t>NON_RECYCLED_WASTE_IN_T</t>
-  </si>
-  <si>
-    <t>Emissions</t>
-  </si>
-  <si>
-    <t>Emissions of Inorganic Pollutants</t>
-  </si>
-  <si>
-    <t>EMISSIONS_OF_INORGANIC_POLLUTANTS_IN_T</t>
-  </si>
-  <si>
-    <t>Emissions of Air Pollutants</t>
-  </si>
-  <si>
-    <t>EMISSIONS_OF_AIR_POLLUTANTS_IN_T</t>
-  </si>
-  <si>
-    <t>Emissions of Ozone Depletion Substances</t>
-  </si>
-  <si>
-    <t>EMISSIONS_OF_OZONE_DEPLETION_SUBSTANCES_IN_T</t>
-  </si>
-  <si>
-    <t>Carbon Reduction Initiatives</t>
-  </si>
-  <si>
-    <t>CARBON_REDUCTION_INITIATIVES</t>
-  </si>
-  <si>
-    <t>Social</t>
-  </si>
-  <si>
-    <t>Social and employee matters</t>
-  </si>
-  <si>
-    <t>Human Rights Legal Proceedings</t>
-  </si>
-  <si>
-    <t>HUMAN_RIGHTS_LEGAL_PROCEEDINGS</t>
-  </si>
-  <si>
-    <t>ILO Core Labour Standards</t>
-  </si>
-  <si>
-    <t>ILO_CORE_LABOUR_STANDARDS</t>
-  </si>
-  <si>
-    <t>Environmental Policy</t>
-  </si>
-  <si>
-    <t>ENVIRONMENTAL_POLICY</t>
-  </si>
-  <si>
-    <t>Existence of an environmental policy.</t>
-  </si>
-  <si>
-    <t>Corruption Legal Proceedings</t>
-  </si>
-  <si>
-    <t>CORRUPTION_LEGAL_PROCEEDINGS</t>
-  </si>
-  <si>
-    <t>Transparency Disclosure Policy</t>
-  </si>
-  <si>
-    <t>TRANSPARENCY_DISCLOSURE_POLICY</t>
-  </si>
-  <si>
-    <t>Existence of a transparency policy. According to the OECD Guidelines for Multinational Enterprises, multinational companies should inform the public not only about their financial performance, but also about all of the important aspects of their business activities, such as how they are meeting social and environmental standards and what risks they foresee linked to their business activities.</t>
-  </si>
-  <si>
-    <t>Human Rights Due Diligence Policy</t>
-  </si>
-  <si>
-    <t>HUMAN_RIGHTS_DUE_DILIGENCE_POLICY</t>
-  </si>
-  <si>
-    <t>Policy against Child Labour</t>
-  </si>
-  <si>
-    <t>POLICY_AGAINST_CHILD_LABOUR</t>
-  </si>
-  <si>
-    <t>Policy against Forced Labour</t>
-  </si>
-  <si>
-    <t>POLICY_AGAINST_FORCED_LABOUR</t>
-  </si>
-  <si>
-    <t>Policy against Discrimination in the Workplace</t>
-  </si>
-  <si>
-    <t>POLICY_AGAINST_DISCRIMINATION_IN_THE_WORKPLACE</t>
-  </si>
-  <si>
-    <t>Existence of policies in place to eliminate discrimination in the workplace.</t>
-  </si>
-  <si>
-    <t>ISO 14001 Certificate</t>
-  </si>
-  <si>
-    <t>ISO_14001_CERTIFICATE</t>
-  </si>
-  <si>
-    <t>Policy against Bribery and Corruption</t>
-  </si>
-  <si>
-    <t>POLICY_AGAINST_BRIBERY_AND_CORRUPTION</t>
-  </si>
-  <si>
-    <t>Fair Business Marketing Advertising Policy</t>
-  </si>
-  <si>
-    <t>FAIR_BUSINESS_MARKETING_ADVERTISING_POLICY</t>
-  </si>
-  <si>
-    <t>Existence of policies and procedures in place to apply fair business, marketing and advertising practices and to guarantee the safety and quality of the goods and services.</t>
-  </si>
-  <si>
-    <t>Technologies Expertise Transfer Policy</t>
-  </si>
-  <si>
-    <t>TECHNOLOGIES_EXPERTISE_TRANSFER_POLICY</t>
-  </si>
-  <si>
-    <t>Existence of policies and procedures in place to permit the transfer and rapid dissemination of technologies and expertise.</t>
-  </si>
-  <si>
-    <t>Fair Competition Policy</t>
-  </si>
-  <si>
-    <t>FAIR_COMPETITION_POLICY</t>
-  </si>
-  <si>
-    <t>Existence of policies and procedures in place related to fair competition and anti-competitive cartels.</t>
-  </si>
-  <si>
-    <t>Violation Of Tax Rules And Regulation</t>
-  </si>
-  <si>
-    <t>VIOLATION_OF_TAX_RULES_AND_REGULATION</t>
-  </si>
-  <si>
-    <t>UN Global Compact Principles Compliance Policy</t>
-  </si>
-  <si>
-    <t>UNGC_PRINCIPLES_COMPLIANCE_POLICY</t>
-  </si>
-  <si>
-    <t>OECD Guidelines For Multinational Enterprises Grievance Handling</t>
-  </si>
-  <si>
-    <t>OECD_GUIDELINES_GRIEVANCE_HANDLING</t>
-  </si>
-  <si>
-    <t>Average Gross Hourly Earnings Male Employees</t>
-  </si>
-  <si>
-    <t>AVG_GROSS_HOURLY_EARNINGS_MALE_EMPLOYEES</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>Average Gross Hourly Earnings Female Employees</t>
-  </si>
-  <si>
-    <t>AVG_GROSS_HOURLY_EARNINGS_FEMALE_EMPLOYEES</t>
-  </si>
-  <si>
-    <t>Unadjusted gender pay gap</t>
-  </si>
-  <si>
-    <t>UNADJUSTED_GENDER_PAY_GAP_PCT</t>
-  </si>
-  <si>
-    <t>Female Board Members - Supervisory Board</t>
-  </si>
-  <si>
-    <t>FEMALE_BOARD_MEMBERS_SUPERVISORY_BOARD</t>
-  </si>
-  <si>
-    <t>Integer</t>
-  </si>
-  <si>
-    <t>Female Board Members - Board of Directors</t>
-  </si>
-  <si>
-    <t>FEMALE_BOARD_MEMBERS_BOARD_OF_DIRECTORS</t>
-  </si>
-  <si>
-    <t>Male Board Members - Supervisory Board</t>
-  </si>
-  <si>
-    <t>MALE_BOARD_MEMBERS_SUPERVISORY_BOARD</t>
-  </si>
-  <si>
-    <t>Male Board Members - Board of Directors</t>
-  </si>
-  <si>
-    <t>MALE_BOARD_MEMBERS_BOARD_OF_DIRECTORS</t>
-  </si>
-  <si>
-    <t>Board gender diversity - Supervisory Board</t>
-  </si>
-  <si>
-    <t>BOARD_GENDER_DIVERSITY_SUPERVISORY_BOARD_PCT</t>
-  </si>
-  <si>
-    <t>Allowed Range: [0, 100]</t>
-  </si>
-  <si>
-    <t>Board gender diversity - Board of Directors</t>
-  </si>
-  <si>
-    <t>BOARD_GENDER_DIVERSITY_BOARD_OF_DIRECTORS_PCT</t>
-  </si>
-  <si>
-    <t>Controversial Weapons Exposure</t>
-  </si>
-  <si>
-    <t>CONTROVERSIAL_WEAPONS_EXPOSURE</t>
-  </si>
-  <si>
-    <t>Workplace Accident Prevention Policy</t>
-  </si>
-  <si>
-    <t>WORKPLACE_ACCIDENT_PREVENTION_POLICY</t>
-  </si>
-  <si>
-    <t>Rate Of Accidents</t>
-  </si>
-  <si>
-    <t>RATE_OF_ACCIDENTS</t>
-  </si>
-  <si>
-    <t>Workdays Lost</t>
-  </si>
-  <si>
-    <t>WORKDAYS_LOST</t>
-  </si>
-  <si>
-    <t>Days</t>
-  </si>
-  <si>
-    <t>Supplier Code Of Conduct</t>
-  </si>
-  <si>
-    <t>SUPPLIER_CODE_OF_CONDUCT</t>
-  </si>
-  <si>
-    <t>Grievance Handling Mechanism</t>
-  </si>
-  <si>
-    <t>GRIEVANCE_HANDLING_MECHANISM</t>
-  </si>
-  <si>
-    <t>Whistleblower Protection Policy</t>
-  </si>
-  <si>
-    <t>WHISTLEBLOWER_PROTECTION_POLICY</t>
-  </si>
-  <si>
-    <t>Reported Incidents Of Discrimination</t>
-  </si>
-  <si>
-    <t>REPORTED_INCIDENTS_OF_DISCRIMINATION</t>
-  </si>
-  <si>
-    <t>Sanctioned Incidents Of Discrimination</t>
-  </si>
-  <si>
-    <t>SANCTIONED_INCIDENTS_OF_DISCRIMINATION</t>
-  </si>
-  <si>
-    <t>Excessive CEO pay ratio</t>
-  </si>
-  <si>
-    <t>EXCESSIVE_CEO_PAY_RATIO</t>
-  </si>
-  <si>
-    <t>Green securities</t>
-  </si>
-  <si>
-    <t>Securities Not Certified As Green</t>
-  </si>
-  <si>
-    <t>SECURITIES_NOT_CERTIFIED_AS_GREEN</t>
-  </si>
-  <si>
-    <t>Possession of securities in investments that are not certified as green under a future EU legal act setting up an EU Green Bond Standard.</t>
-  </si>
-  <si>
-    <t>Human rights</t>
-  </si>
-  <si>
-    <t>Human Rights Policy</t>
-  </si>
-  <si>
-    <t>HUMAN_RIGHTS_POLICY</t>
-  </si>
-  <si>
-    <t>Human Rights Due Diligence</t>
-  </si>
-  <si>
-    <t>HUMAN_RIGHTS_DUE_DILIGENCE</t>
-  </si>
-  <si>
-    <t>Trafficking In Human Beings Policy</t>
-  </si>
-  <si>
-    <t>TRAFFICKING_IN_HUMAN_BEINGS_POLICY</t>
-  </si>
-  <si>
-    <t>Reported Child Labour Incidents</t>
-  </si>
-  <si>
-    <t>REPORTED_CHILD_LABOUR_INCIDENTS</t>
-  </si>
-  <si>
-    <t>Reported Forced Or Compulsory Labour Incidents</t>
-  </si>
-  <si>
-    <t>REPORTED_FORCED_OR_COMPULSORY_LABOUR_INCIDENTS</t>
-  </si>
-  <si>
-    <t>Number Of Reported Incidents Of Human Rights Violations</t>
-  </si>
-  <si>
-    <t>NO_OF_REPORTED_INCIDENTS_OF_HUMAN_RIGHTS_VIOLATIONS</t>
-  </si>
-  <si>
-    <t>Anti-corruption and anti-bribery</t>
-  </si>
-  <si>
-    <t>Cases of Insufficient Action against Bribery and Corruption</t>
-  </si>
-  <si>
-    <t>CASES_OF_INSUFFICIENT_ACTION_AGAINST_BRIBERY_AND_CORRUPTION</t>
-  </si>
-  <si>
-    <t>Reported Convictions Of Bribery and Corruption</t>
-  </si>
-  <si>
-    <t>REPORTED_CONVICTIONS_OF_BRIBERY_AND_CORRUPTION</t>
-  </si>
-  <si>
-    <t>Total Amount Of Reported Fines Of Bribery and Corruption</t>
-  </si>
-  <si>
-    <t>TOTAL_AMOUNT_OF_REPORTED_FINES_OF_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
     <t>Scope 1 greenhouse gas emissions, namely emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used). See also Regulation (EU) 2016/1011 Annex III (1)(e)(i).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
   </si>
   <si>
+    <t>Tonnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greenhouse gas emissions </t>
+  </si>
+  <si>
+    <t>Scope 2 GHG emissions</t>
+  </si>
+  <si>
+    <t>SCOPE_2_GHG_EMISSIONS_IN_T</t>
+  </si>
+  <si>
     <t>Scope 2 greenhouse gas emissions, namely emissions from the consumption of purchased electricity, steam, or other sources of energy generated upstream from the company that issues the underlying assets (preferably using the location-based method and equity share approach). See also (EU) 2016/1011 Annex III (1)(e)(ii).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
   </si>
   <si>
+    <t>Scope 2 GHG emissions (location-based)</t>
+  </si>
+  <si>
+    <t>SCOPE_2_GHG_EMISSIONS_LOCATION_IN_T</t>
+  </si>
+  <si>
     <t>Scope 2 greenhouse gas emissions computed using the location-based method (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(ii).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
   </si>
   <si>
+    <t>Scope 2 GHG emissions (market-based)</t>
+  </si>
+  <si>
+    <t>SCOPE_2_GHG_EMISSIONS_MARKET_IN_T</t>
+  </si>
+  <si>
     <t>Scope 2 greenhouse gas emissions computed using the market-based method (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(ii).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
   </si>
   <si>
+    <t>Scope 1 and 2 GHG emissions</t>
+  </si>
+  <si>
+    <t>SCOPE_1_2_GHG_EMISSIONS_IN_T</t>
+  </si>
+  <si>
     <t>Sum of scope 1 and 2 greenhouse gas emissions (computed preferably using the location-based method and equity share approach). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
   </si>
   <si>
+    <t>Scope 1 and 2 GHG emissions (location-based)</t>
+  </si>
+  <si>
+    <t>SCOPE_1_2_GHG_EMISSIONS_LOCATION_IN_T</t>
+  </si>
+  <si>
     <t>Sum of scope 1 and 2 greenhouse gas emissions, using the location-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
   </si>
   <si>
+    <t>Scope 1 and 2 GHG emissions (market-based)</t>
+  </si>
+  <si>
+    <t>SCOPE_1_2_GHG_EMISSIONS_MARKET_IN_T</t>
+  </si>
+  <si>
     <t>Sum of scope 1 and 2 greenhouse gas emissions, using the market-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
   </si>
   <si>
+    <t>Scope 3 GHG emissions</t>
+  </si>
+  <si>
+    <t>SCOPE_3_GHG_EMISSIONS_IN_T</t>
+  </si>
+  <si>
     <t>Scope 3 greenhouse gas emissions in tons, i.e., all indirect upstream and downstream emissions that are neither covered by scope 1 ghg emissions nor by scope 2 ghg emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(iii).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
   </si>
   <si>
+    <t>Scope 3 upstream GHG emissions</t>
+  </si>
+  <si>
+    <t>SCOPE_3_UPSTREAM_GHG_EMISSIONS_IN_T</t>
+  </si>
+  <si>
     <t>Indirect (gross) scope 3 greenhouse gas emissions from activities related to the production and distribution of goods and services purchased by the reporting company (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(iii).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
   </si>
   <si>
+    <t>Scope 3 downstream GHG emissions</t>
+  </si>
+  <si>
+    <t>SCOPE_3_DOWNSTREAM_GHG_EMISSIONS_IN_T</t>
+  </si>
+  <si>
     <t>Indirect (gross) scope 3 greenhouse gas emissions that occur as a result of the use or disposal of the reporting company’s sold products and services (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(iii).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
   </si>
   <si>
+    <t>Scope 1 and 2 and 3 GHG emissions</t>
+  </si>
+  <si>
+    <t>SCOPE_1_2_3_GHG_EMISSIONS_IN_T</t>
+  </si>
+  <si>
     <t>Sum of scope 1, 2 and 3 greenhouse gas emissions (computed preferably using the location-based method and equity share). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii)+(iii) and Regulation (EU) 2022/1288, Annex I, top (4) and formula (2)+(3).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
   </si>
   <si>
+    <t>Scope 1 and 2 and 3 GHG emissions (location-based)</t>
+  </si>
+  <si>
+    <t>SCOPE_1_2_3_GHG_EMISSIONS_LOCATION_IN_T</t>
+  </si>
+  <si>
     <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the location-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii)+(iii).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
   </si>
   <si>
+    <t>Scope 1 and 2 and 3 GHG emissions (market-based)</t>
+  </si>
+  <si>
+    <t>SCOPE_1_2_3_GHG_EMISSIONS_MARKET_IN_T</t>
+  </si>
+  <si>
     <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the market-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii)+(iii).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
   </si>
   <si>
-    <t>The enterprise value in EUR, i.e. the sum, at fiscal year-end, of the market capitalisation of ordinary shares, the market capitalisation of preferred shares, the book value of total debt and non-controlling interests, without the deduction of cash or cash equivalents. See also Regulation (EU) 2022/1288, Annex I, top (4) and formula (1)+(2).
-Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2</t>
-  </si>
-  <si>
-    <t>Total net or gross revenue in EUR for the financial year. i.e., income arising in the course of an entity's ordinary activities, the amounts derived from the sale of products and the provision of services. Overall turnover is equivalent to a firm's total revenues over some period of time. See also Regulation (EU) 2022/1288, Annex I, formula (3).
-Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+    <t>Carbon footprint</t>
+  </si>
+  <si>
+    <t>CARBON_FOOTPRINT_IN_T_PER_MIO_EUR_ENTERPRISE_VALUE</t>
   </si>
   <si>
     <t>Tons of GHG emissions per million EUR enterprise value. See also (EU) 2022/1288 Annex I formula (2).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 2</t>
   </si>
   <si>
+    <t>Tonnes / €M Enterprise Value</t>
+  </si>
+  <si>
+    <t>GHG intensity</t>
+  </si>
+  <si>
+    <t>GHG_INTENSITY_IN_T_PER_MIO_EUR_REVENUE</t>
+  </si>
+  <si>
     <t>Tons of GHG emissions per million EUR revenue, preferably calculated using the location-based method and the equity share approach for emissions. See also Regulation (EU) 2022/1288, Annex I, formula (3).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
   </si>
   <si>
+    <t>Tonnes / €M Revenue</t>
+  </si>
+  <si>
+    <t>GHG intensity - scope 1</t>
+  </si>
+  <si>
+    <t>GHG_INTENSITY_SCOPE_1_IN_T_PER_MIO_EUR_REVENUE</t>
+  </si>
+  <si>
     <t>Tons of scope 1 GHG emissions per million EUR revenue. Scope 1 carbon emissions are emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used for emissions). See also Regulation (EU) 2022/1288, Annex I, formula (3).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
   </si>
   <si>
+    <t>GHG intensity - scope 2</t>
+  </si>
+  <si>
+    <t>GHG_INTENSITY_SCOPE_2_IN_T_PER_MIO_EUR_REVENUE</t>
+  </si>
+  <si>
     <t>Tons of scope 2 GHG emissions per million EUR revenue. Scope 2 emissions refer to those generated from the consumption of purchased electricity, steam, or other energy sources produced upstream by external entities or companies. Preferably, these should be calculated using the location-based method and the equity share approach for emissions. See also Regulation (EU) 2022/1288, Annex I, formula (3).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
   </si>
   <si>
+    <t>GHG intensity - scope 3</t>
+  </si>
+  <si>
+    <t>GHG_INTENSITY_SCOPE_3_IN_T_PER_MIO_EUR_REVENUE</t>
+  </si>
+  <si>
     <t>Tons of scope 3 GHG emissions per million EUR revenue. Scope 3 emissions encompass all indirect upstream and downstream emissions not covered by Scope 2. Preferably, the equity share approach should be used for calculating these emissions. See also Regulation (EU) 2022/1288, Annex I, formula (3).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
   </si>
   <si>
+    <t>Fossil Fuel Sector Exposure</t>
+  </si>
+  <si>
+    <t>FOSSIL_FUEL_SECTOR_EXPOSURE</t>
+  </si>
+  <si>
     <t>(Part of) revenues derived from exploration, mining, extraction, production, processing, storage, refining or distribution, including transportation, storage and trade, of fossil fuels. (Fossil fuels mean non-renewable carbon-based energy sources such as solid fuels, natural gas and oil.) See also Regulation (EU) 2022/1288, Annex I, top (5).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 4</t>
   </si>
   <si>
+    <t>Yes/No</t>
+  </si>
+  <si>
+    <t>Financed scope 1 and scope 2 emissions</t>
+  </si>
+  <si>
+    <t>FINANCED_SCOPE_1_2_EMISSIONS_IN_T</t>
+  </si>
+  <si>
     <t>The sum of scope 1 and scope 2 emissions of financed companies.
 Is part of scope 3 emissions and can be reported in Category 15 (Investments).</t>
   </si>
   <si>
+    <t xml:space="preserve">Tonnes </t>
+  </si>
+  <si>
+    <t>Financed scope 3 emissions</t>
+  </si>
+  <si>
+    <t>FINANCED_SCOPE_3_EMISSIONS_IN_T</t>
+  </si>
+  <si>
     <t>The scope 3 emissions of financed companies.
 Is part of scope 3 emissions and can be reported in Category 15 (Investments).</t>
   </si>
   <si>
+    <t>Energy performance</t>
+  </si>
+  <si>
+    <t>Renewable Energy Production</t>
+  </si>
+  <si>
+    <t>RENEWABLE_ENERGY_PROD_IN_GWH</t>
+  </si>
+  <si>
     <t>Total value of renewable energy produced, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
   </si>
   <si>
+    <t>GWh</t>
+  </si>
+  <si>
+    <t>Renewable Energy Consumption</t>
+  </si>
+  <si>
+    <t>RENEWABLE_ENERGY_CONS_IN_GWH</t>
+  </si>
+  <si>
     <t>Total value of renewable energy consumed, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
   </si>
   <si>
+    <t>Non-Renewable Energy Production</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_PROD_IN_GWH</t>
+  </si>
+  <si>
     <t>Total value of non-renewable energy produced, meaning energy from sources other than renewable sources. See also Regulation (EU) 2022/1288, Annex I, top (7).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
   </si>
   <si>
+    <t>Relative Non-Renewable Energy Production</t>
+  </si>
+  <si>
+    <t>REL_NON_RENEWABLE_ENERGY_PROD_PCT</t>
+  </si>
+  <si>
     <t>Share of non-renewable energy production from total energy production (i.e. renewable plus non-renewable). See also Regulation (EU) 2022/1288, Annex I, top (7).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
   </si>
   <si>
+    <t>Percent</t>
+  </si>
+  <si>
+    <t>Non-Renewable Energy Consumption</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_IN_GWH</t>
+  </si>
+  <si>
     <t>Total value of non-renewable energy consumed, meaning energy from sources other than renewable sources. See also Regulation (EU) 2022/1288, Annex I, top (7).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
   </si>
   <si>
+    <t>Relative Non-Renewable Energy Consumption</t>
+  </si>
+  <si>
+    <t>REL_NON_RENEWABLE_ENERGY_CONS_PCT</t>
+  </si>
+  <si>
     <t>Share of non-renewable energy consumption from total energy consumption (i.e. renewable plus non-renewable). See also Regulation (EU) 2022/1288, Annex I, top (7).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
   </si>
   <si>
-    <t>Sector applicable activities. See also Regulation (EU) 2022/1288, Annex I, top (9).
-Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 6</t>
+    <t>Total High Impact Climate Sector Energy Consumption</t>
+  </si>
+  <si>
+    <t>TOTAL_HIGH_IMPACT_CLIMATE_SECTOR_ENERGY_CONS_IN_GWH</t>
   </si>
   <si>
     <t>"High impact climate sectors" refers to the sectors outlined in Sections A to H and Section L of Annex I of Regulation (EC) No 1893/2006 by the European Parliament and Council. This regulation, established on 20 December 2006, provides the statistical classification of economic activities known as NACE Revision 2 and amends Council Regulation (EEC) No 3037/90 and certain EC regulations related to specific statistical areas (OJ L 393, 30.12.2006, p. 1). See also Regulation (EU) 2022/1288, Annex I, top (9).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 6</t>
   </si>
   <si>
+    <t>Non-Renewable Energy Consumption Fossil Fuels</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_FOSSIL_FUELS_IN_GWH</t>
+  </si>
+  <si>
     <t>Energy consumption from fossil fuels (sum of crude oil, natural gas, lignite and coal, etc.) (non-renewable energy source).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
   </si>
   <si>
+    <t>Non-Renewable Energy Consumption Crude Oil</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_CRUDE_OIL_IN_GWH</t>
+  </si>
+  <si>
     <t>Energy consumption from crude oil (including petrol, diesel, fuel oil and others) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
   </si>
   <si>
+    <t>Non-Renewable Energy Consumption Natural Gas</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_NATURAL_GAS_IN_GWH</t>
+  </si>
+  <si>
     <t>Energy consumption from natural gas (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
   </si>
   <si>
+    <t>Non-Renewable Energy Consumption Lignite</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_LIGNITE_IN_GWH</t>
+  </si>
+  <si>
     <t>Energy consumption from lignite (non-renewable energy source) Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
   </si>
   <si>
+    <t>Non-Renewable Energy Consumption Coal</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_COAL_IN_GWH</t>
+  </si>
+  <si>
     <t>Energy consumption from coal (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
   </si>
   <si>
+    <t>Non-Renewable Energy Consumption Nuclear Energy</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_NUCLEAR_ENERGY_IN_GWH</t>
+  </si>
+  <si>
     <t>Energy consumption from nuclear energy (Uranium) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
   </si>
   <si>
+    <t>Non-Renewable Energy Consumption Other</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_OTHER_IN_GWH</t>
+  </si>
+  <si>
     <t>Energy consumption from any other available (used) non-renewable source of energy. Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Biodiversity</t>
+  </si>
+  <si>
+    <t>Primary Forest And Wooded Land Of Native Species Exposure</t>
+  </si>
+  <si>
+    <t>PRIMARY_FOREST_AND_WOODED_LAND_OF_NATIVE_SPECIES_EXPOSURE</t>
   </si>
   <si>
     <t>Sites or operations that are located, either partially or entirely, in or near primary forests and other wooded areas where their activities have a negative impact on these environments. See also Regulation (EU) 2022/1288, Annex I, top (19).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
   </si>
   <si>
-    <r>
-      <t>Sites or operations that are partially or fully located in or near protected or biodiversity-sensitive areas, where their activities adversely impact these regions.</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
-    </r>
+    <t>Protected Areas Exposure</t>
+  </si>
+  <si>
+    <t>PROTECTED_AREAS_EXPOSURE</t>
+  </si>
+  <si>
+    <t>Sites or operations that are partially or fully located in or near protected or biodiversity-sensitive areas, where their activities adversely impact these regions.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
+  </si>
+  <si>
+    <t>Rare Or Endangered Ecosystems Exposure</t>
+  </si>
+  <si>
+    <t>RARE_OR_ENDANGERED_ECOSYSTEMS_EXPOSURE</t>
   </si>
   <si>
     <t>Sites or operations located in or near areas designated for the protection of species, including flora and fauna, where their activities lead to the deterioration of natural habitats and disturb the species for which these areas have been designated. See also Regulation (EU) 2022/1288, Annex I, top 18(a).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
   </si>
   <si>
-    <t>Sites or operations that are partially or fully situated in areas of highly biodiverse grassland, which may be categorized as either: (i) natural grassland, meaning areas that would remain grassland without human intervention and preserve natural species composition and ecological characteristics; or (ii) non-natural grassland, meaning areas that would no longer be grassland without human intervention but are species-rich and not degraded, unless it is demonstrated that harvesting the raw material is essential to maintain its grassland status.
-Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
+    <t>Manufacture Of Agrochemical Pesticides Products</t>
+  </si>
+  <si>
+    <t>MANUFACTURE_OF_AGROCHEMICAL_PESTICIDES_PRODUCTS</t>
   </si>
   <si>
     <t>Involvements in manufacture of pesticides and other agrochemical products. See Regulation (EC) No 1893/2006, Annex I, Division 20.2.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 9</t>
   </si>
   <si>
+    <t>Land Degradation Desertification Soil Sealing</t>
+  </si>
+  <si>
+    <t>LAND_DEGRADATION_DESERTIFICATION_SOIL_SEALING</t>
+  </si>
+  <si>
     <t>Involvement in activities, which cause land degradation, desertification or soil sealing.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 10</t>
   </si>
   <si>
-    <r>
-      <t>Existence of sustainable land or agriculture practices or policies.</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 11</t>
-    </r>
+    <t>Sustainable Agriculture Policy</t>
+  </si>
+  <si>
+    <t>SUSTAINABLE_AGRICULTURE_POLICY</t>
+  </si>
+  <si>
+    <t>Existence of sustainable land or agriculture practices or policies.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 11</t>
+  </si>
+  <si>
+    <t>Sustainable Oceans And Seas Policy</t>
+  </si>
+  <si>
+    <t>SUSTAINABLE_OCEANS_AND_SEAS_POLICY</t>
   </si>
   <si>
     <t>Existence of sustainable oceans or seas practices or policies.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 12</t>
   </si>
   <si>
+    <t>Threatened Species Exposure</t>
+  </si>
+  <si>
+    <t>THREATENED_SPECIES_EXPOSURE</t>
+  </si>
+  <si>
     <t>Operations, which affect threatened species. See also Regulation (EU) 2022/1288, Annex I, top (20).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 14.1</t>
   </si>
   <si>
+    <t>Biodiversity Protection Policy</t>
+  </si>
+  <si>
+    <t>BIODIVERSITY_PROTECTION_POLICY</t>
+  </si>
+  <si>
     <t>Existence of a biodiversity protection policy that encompasses operational sites owned, leased, managed in, or adjacent to a protected area or an area of high biodiversity value outside protected areas.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 14.2</t>
   </si>
   <si>
-    <r>
-      <t>Existence of a policy to address deforestation. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See also Regulation (EU) 2022/1288, Annex I, top (21).</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 15</t>
-    </r>
+    <t>Deforestation Policy</t>
+  </si>
+  <si>
+    <t>DEFORESTATION_POLICY</t>
+  </si>
+  <si>
+    <t>Existence of a policy to address deforestation. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See also Regulation (EU) 2022/1288, Annex I, top (21).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 15</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Emissions To Water</t>
+  </si>
+  <si>
+    <t>EMISSIONS_TO_WATER_IN_T</t>
   </si>
   <si>
     <t>Emissions to water in tons (direct emissions of priority substances as defined in Article 2(30) of Directive 2000/60/EC of the European Parliament and of the Council and direct emissions of nitrates, phosphates and pesticides). See Regulation (EU) 2022/1288, Annex I, top (12).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 8</t>
   </si>
   <si>
+    <t>Water Withdrawal</t>
+  </si>
+  <si>
+    <t>WATER_WITHDRAWAL_IN_M3</t>
+  </si>
+  <si>
     <t>Amount of water withdrawn by the company.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 6.1</t>
   </si>
   <si>
+    <t>Cubic Meters</t>
+  </si>
+  <si>
+    <t>Water Reused</t>
+  </si>
+  <si>
+    <t>WATER_REUSED_IN_M3</t>
+  </si>
+  <si>
     <t>Amount of water recycled or reused by the company.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 6.1</t>
   </si>
   <si>
+    <t>Water Withdrawal Intensity</t>
+  </si>
+  <si>
+    <t>REL_WATER_WITHDRAWAL_INTENSITY_IN_M3_PER_MIO_EUR_REVENUE</t>
+  </si>
+  <si>
     <t>Amount in cubic meters of water withdrawn per million EUR revenue.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 6.1</t>
   </si>
   <si>
+    <t>Cubic Meters / €M Revenue</t>
+  </si>
+  <si>
+    <t>Water Management Policy</t>
+  </si>
+  <si>
+    <t>WATER_MANAGEMENT_POLICY</t>
+  </si>
+  <si>
     <t>Existence of a policy for water management.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factors 7, 8</t>
   </si>
   <si>
-    <r>
-      <t>Sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy.</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 8</t>
-    </r>
+    <t>High Water Stress Area Exposure</t>
+  </si>
+  <si>
+    <t>HIGH_WATER_STRESS_AREA_EXPOSURE</t>
+  </si>
+  <si>
+    <t>Sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 8</t>
+  </si>
+  <si>
+    <t>Waste</t>
+  </si>
+  <si>
+    <t>Hazardous and Radioactive Waste</t>
+  </si>
+  <si>
+    <t>HAZARDOUS_AND_RADIOACTIVE_WASTE_IN_T</t>
   </si>
   <si>
     <t>Tons of hazardous waste and radioactive waste generated: Hazardous waste are Explosives, Oxidizing substances, Highly flammable, Flammable, Irritant Harmful, Toxic, Carcinogenic, Corrosive, Infectious, Toxic for reproduction, Mutagenic, waste which releases toxic or very toxic gases in contact with water, air or an acid, Sensitizing, Ecotoxic, waste capable by any means after disposal of yielding another substance which possesses any of the characteristics listed above. Radioactive waste means radioactive material in gaseous, liquid or solid form for which no further use is foreseen. See Regulation (EU) 2022/1288, Annex I, top (14)-(16), Directive 2008/98/EC Annex III and Council Directive 2011/70/Euratom, Article 3 (7).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 9</t>
   </si>
   <si>
+    <t>Non-Recycled Waste</t>
+  </si>
+  <si>
+    <t>NON_RECYCLED_WASTE_IN_T</t>
+  </si>
+  <si>
     <t>Tons of non-recycled waste generated. "Non-recycled waste" means any waste not recycled within the meaning of ‘recycling’ in Article 3(17) of Directive 2008/98/EC. See Regulation (EU) 2022/1288, Annex I, top (17).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 13</t>
   </si>
   <si>
+    <t>Emissions</t>
+  </si>
+  <si>
+    <t>Emissions of Inorganic Pollutants</t>
+  </si>
+  <si>
+    <t>EMISSIONS_OF_INORGANIC_POLLUTANTS_IN_T</t>
+  </si>
+  <si>
     <t>Tons of emissions by inorganic pollutants. Inorganic pollutants include substances like arsenic, cadmium, lead, mercury, chromium, aluminium, nitrates, nitrites, fluorides, and water contaminants such as arsenic, fluoride, nitrate, and heavy metals. See Regulation (EU) 2022/1288, Annex I, top (27).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 1</t>
   </si>
   <si>
+    <t>Emissions of Air Pollutants</t>
+  </si>
+  <si>
+    <t>EMISSIONS_OF_AIR_POLLUTANTS_IN_T</t>
+  </si>
+  <si>
     <t>Tons of emissions by air pollutants. Emissions by air pollutants include direct sulphur oxides (Sox/SO2) emissions, direct nitrogen oxides (NOx/NO2) emissions, direct ammonia (NH3) emissions, direct particulate matter (PM2.5) emissions, direct non-methane volatile organic compounds (NMVOC) emissions and direct total heavy metals (HM) emissions (encompassing cadmium, mercury and lead). See Regulation (EU) 2022/1288, Annex I, top (28) and Directive (EU) 2016/2284, Article 3, points (5)-(8) and Annex I, table A.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 2</t>
   </si>
   <si>
+    <t>Emissions of Ozone Depletion Substances</t>
+  </si>
+  <si>
+    <t>EMISSIONS_OF_OZONE_DEPLETION_SUBSTANCES_IN_T</t>
+  </si>
+  <si>
     <t>Tons of ozone depletion substances, chemicals that destroy the earth's protective ozone layer. They include: chlorofluorocarbons (CFCs), halons, carbon tetrachloride (CCl4), methyl chloroform (CH3CCl3), hydrobromofluorocarbons (HBFCs), hydrochlorofluorocarbons (HCFCs), methyl bromide (CH3Br), bromochloromethane (CH2BrCl), hydrofluorocarbons (HFCs). See Regulation (EU) 2022/1288, Annex I, top (29) and the Montreal Protocol on Substances that Deplete the Ozone Layer.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 3</t>
   </si>
   <si>
+    <t>Carbon Reduction Initiatives</t>
+  </si>
+  <si>
+    <t>CARBON_REDUCTION_INITIATIVES</t>
+  </si>
+  <si>
     <t>Existence of policies or procedures for carbon emission reduction aimed at aligning with the Paris Agreement.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 4</t>
   </si>
   <si>
+    <t>Social</t>
+  </si>
+  <si>
+    <t>Social and employee matters</t>
+  </si>
+  <si>
+    <t>Human Rights Legal Proceedings</t>
+  </si>
+  <si>
+    <t>HUMAN_RIGHTS_LEGAL_PROCEEDINGS</t>
+  </si>
+  <si>
     <t>Involvement in Human Rights related legal proceedings.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 14</t>
   </si>
   <si>
+    <t>ILO Core Labour Standards</t>
+  </si>
+  <si>
+    <t>ILO_CORE_LABOUR_STANDARDS</t>
+  </si>
+  <si>
     <t>Abidance by the ILO Core Labour Standards.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factors 12, 13, 14</t>
   </si>
   <si>
+    <t>Environmental Policy</t>
+  </si>
+  <si>
+    <t>ENVIRONMENTAL_POLICY</t>
+  </si>
+  <si>
+    <t>Existence of an environmental policy.</t>
+  </si>
+  <si>
+    <t>Corruption Legal Proceedings</t>
+  </si>
+  <si>
+    <t>CORRUPTION_LEGAL_PROCEEDINGS</t>
+  </si>
+  <si>
     <t>Involvement in corruption-related legal proceedings.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 16</t>
   </si>
   <si>
+    <t>Human Rights Due Diligence Policy</t>
+  </si>
+  <si>
+    <t>HUMAN_RIGHTS_DUE_DILIGENCE_POLICY</t>
+  </si>
+  <si>
     <t>Existence of policies in place to support/respect human rights and carry out due diligence to ensure that the business activities do not have a negative human rights impact.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 10</t>
   </si>
   <si>
+    <t>Policy against Child Labour</t>
+  </si>
+  <si>
+    <t>POLICY_AGAINST_CHILD_LABOUR</t>
+  </si>
+  <si>
     <t>Existence of policies in place to abolish all forms of child labour.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 12</t>
   </si>
   <si>
+    <t>Policy against Forced Labour</t>
+  </si>
+  <si>
+    <t>POLICY_AGAINST_FORCED_LABOUR</t>
+  </si>
+  <si>
     <t>Existence of policies in place to abolish all forms of forced labour.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 13</t>
   </si>
   <si>
-    <t>The whole company is ISO 14001 certified.</t>
+    <t>Policy against Discrimination in the Workplace</t>
+  </si>
+  <si>
+    <t>POLICY_AGAINST_DISCRIMINATION_IN_THE_WORKPLACE</t>
+  </si>
+  <si>
+    <t>Existence of policies in place to eliminate discrimination in the workplace.</t>
+  </si>
+  <si>
+    <t>Policy against Bribery and Corruption</t>
+  </si>
+  <si>
+    <t>POLICY_AGAINST_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
     <t>Existence of a policy on anti-corruption and anti-bribery consistent with the United Nations Convention against Corruption.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 15</t>
   </si>
   <si>
+    <t>Fair Business Marketing Advertising Policy</t>
+  </si>
+  <si>
+    <t>FAIR_BUSINESS_MARKETING_ADVERTISING_POLICY</t>
+  </si>
+  <si>
+    <t>Existence of policies and procedures in place to apply fair business, marketing and advertising practices and to guarantee the safety and quality of the goods and services.</t>
+  </si>
+  <si>
+    <t>Fair Competition Policy</t>
+  </si>
+  <si>
+    <t>FAIR_COMPETITION_POLICY</t>
+  </si>
+  <si>
+    <t>Existence of policies and procedures in place related to fair competition and anti-competitive cartels.</t>
+  </si>
+  <si>
+    <t>Violation Of UNGC Principles And OECD Guidelines</t>
+  </si>
+  <si>
+    <t>VIOLATION_OF_UNGC_PRINCIPLES_AND_OECD_GUIDELINES</t>
+  </si>
+  <si>
     <t>Involvement in a violation of the UNGC principles or OECD Guidelines for Multinational Enterprises.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 10</t>
   </si>
   <si>
-    <r>
-      <t>Existence of a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises.</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 11</t>
-    </r>
+    <t>UN Global Compact Principles Compliance Policy</t>
+  </si>
+  <si>
+    <t>UNGC_PRINCIPLES_COMPLIANCE_POLICY</t>
+  </si>
+  <si>
+    <t>Existence of a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 11</t>
+  </si>
+  <si>
+    <t>OECD Guidelines For Multinational Enterprises Grievance Handling</t>
+  </si>
+  <si>
+    <t>OECD_GUIDELINES_GRIEVANCE_HANDLING</t>
   </si>
   <si>
     <t>Existence of grievance/complaints handling mechanisms to address violations of the UNGC principles or OECD Guidelines for Multinational Enterprises.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 11</t>
   </si>
   <si>
-    <t>Average gross hourly earnings of male employees
-Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 12</t>
-  </si>
-  <si>
-    <t>Average gross hourly earnings of female employees
-Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 12</t>
+    <t>Unadjusted gender pay gap</t>
+  </si>
+  <si>
+    <t>UNADJUSTED_GENDER_PAY_GAP_PCT</t>
   </si>
   <si>
     <t>(average gross hourly earnings of male paid employees - average gross hourly earnings of female paid employees)/ average gross hourly earnings of male paid employees (in Percent). See Regulation (EU) 2022/1288, Annex I, top (23).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 12</t>
   </si>
   <si>
+    <t>Female Board Members - Supervisory Board</t>
+  </si>
+  <si>
+    <t>FEMALE_BOARD_MEMBERS_SUPERVISORY_BOARD</t>
+  </si>
+  <si>
     <t>Number of females on the supervisory board, i.e. means the administrative, management or supervisory body of a company
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
   </si>
   <si>
+    <t>Integer</t>
+  </si>
+  <si>
+    <t>Female Board Members - Board of Directors</t>
+  </si>
+  <si>
+    <t>FEMALE_BOARD_MEMBERS_BOARD_OF_DIRECTORS</t>
+  </si>
+  <si>
     <t>Number of females on the board of directors of the company
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
   </si>
   <si>
+    <t>Male Board Members - Supervisory Board</t>
+  </si>
+  <si>
+    <t>MALE_BOARD_MEMBERS_SUPERVISORY_BOARD</t>
+  </si>
+  <si>
     <t>Number of males on the supervisory board, i.e. means the administrative, management or supervisory body of a company
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
   </si>
   <si>
+    <t>Male Board Members - Board of Directors</t>
+  </si>
+  <si>
+    <t>MALE_BOARD_MEMBERS_BOARD_OF_DIRECTORS</t>
+  </si>
+  <si>
     <t>Number of males on the board of directors of the company
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
   </si>
   <si>
+    <t>Board gender diversity - Supervisory Board</t>
+  </si>
+  <si>
+    <t>BOARD_GENDER_DIVERSITY_SUPERVISORY_BOARD_PCT</t>
+  </si>
+  <si>
     <t>Percentage of female board members among all supervisory board members.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
   </si>
   <si>
+    <t>Allowed Range: [0, 100]</t>
+  </si>
+  <si>
+    <t>Board gender diversity - Board of Directors</t>
+  </si>
+  <si>
+    <t>BOARD_GENDER_DIVERSITY_BOARD_OF_DIRECTORS_PCT</t>
+  </si>
+  <si>
     <t>Percentage of female board members among all board of directors members.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
   </si>
   <si>
-    <r>
-      <t>Involvement in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons.</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 14</t>
-    </r>
+    <t>Controversial Weapons Exposure</t>
+  </si>
+  <si>
+    <t>CONTROVERSIAL_WEAPONS_EXPOSURE</t>
+  </si>
+  <si>
+    <t>Involvement in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 14</t>
+  </si>
+  <si>
+    <t>Workplace Accident Prevention Policy</t>
+  </si>
+  <si>
+    <t>WORKPLACE_ACCIDENT_PREVENTION_POLICY</t>
   </si>
   <si>
     <t>Existence of a workplace accident prevention policy.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 1</t>
   </si>
   <si>
+    <t>Rate Of Accidents</t>
+  </si>
+  <si>
+    <t>RATE_OF_ACCIDENTS</t>
+  </si>
+  <si>
     <t>Rate of recordable work-related injuries as defined in GRI, i.e. (Number of recordable work-related injuries) /  (number of hours worked ) x 200,000.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 2</t>
   </si>
   <si>
-    <r>
-      <t>Number of workdays lost to injuries, accidents, fatalities or illness in total.</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Existence of a supplier code of conduct addressing unsafe working conditions, precarious work, child labour, and forced labour.</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 4</t>
-    </r>
+    <t>Workdays Lost</t>
+  </si>
+  <si>
+    <t>WORKDAYS_LOST</t>
+  </si>
+  <si>
+    <t>Number of workdays lost to injuries, accidents, fatalities or illness in total.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 3</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>Supplier Code Of Conduct</t>
+  </si>
+  <si>
+    <t>SUPPLIER_CODE_OF_CONDUCT</t>
+  </si>
+  <si>
+    <t>Existence of a supplier code of conduct addressing unsafe working conditions, precarious work, child labour, and forced labour.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 4</t>
+  </si>
+  <si>
+    <t>Grievance Handling Mechanism</t>
+  </si>
+  <si>
+    <t>GRIEVANCE_HANDLING_MECHANISM</t>
   </si>
   <si>
     <t>Existence of a grievance/complaints handling mechanism related to employee matters.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 5</t>
   </si>
   <si>
+    <t>Whistleblower Protection Policy</t>
+  </si>
+  <si>
+    <t>WHISTLEBLOWER_PROTECTION_POLICY</t>
+  </si>
+  <si>
     <t>Existence of a policy on the protection of whistleblowers. See also Regulation (EU) 2022/1288, Annex I, top (26).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 6</t>
   </si>
   <si>
+    <t>Reported Incidents Of Discrimination</t>
+  </si>
+  <si>
+    <t>REPORTED_INCIDENTS_OF_DISCRIMINATION</t>
+  </si>
+  <si>
     <t>Number of reported discrimination-related incidents.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 7.1</t>
   </si>
   <si>
-    <r>
-      <t>Number of discrimination related incidents reported that lead to any kind of penalty and/or fine.</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 7.2</t>
-    </r>
+    <t>Sanctioned Incidents Of Discrimination</t>
+  </si>
+  <si>
+    <t>SANCTIONED_INCIDENTS_OF_DISCRIMINATION</t>
+  </si>
+  <si>
+    <t>Number of discrimination related incidents reported that lead to any kind of penalty and/or fine.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 7.2</t>
+  </si>
+  <si>
+    <t>Excessive CEO pay ratio</t>
+  </si>
+  <si>
+    <t>EXCESSIVE_CEO_PAY_RATIO</t>
   </si>
   <si>
     <t>Annual total compensation for the highest compensated individual divided by the median annual total compensation for all employees (excluding the highest-compensated individual).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 8</t>
   </si>
   <si>
+    <t>Human rights</t>
+  </si>
+  <si>
+    <t>Human Rights Policy</t>
+  </si>
+  <si>
+    <t>HUMAN_RIGHTS_POLICY</t>
+  </si>
+  <si>
     <t>Existence of a human rights policy.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 9</t>
   </si>
   <si>
+    <t>Human Rights Due Diligence</t>
+  </si>
+  <si>
+    <t>HUMAN_RIGHTS_DUE_DILIGENCE</t>
+  </si>
+  <si>
     <t>Existence of due diligence processes to identify, prevent, mitigate and address adverse human rights impacts.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 10</t>
   </si>
   <si>
-    <r>
-      <t>Existence of a policy against trafficking in human beings.</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 11</t>
-    </r>
+    <t>Trafficking In Human Beings Policy</t>
+  </si>
+  <si>
+    <t>TRAFFICKING_IN_HUMAN_BEINGS_POLICY</t>
+  </si>
+  <si>
+    <t>Existence of a policy against trafficking in human beings.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 11</t>
+  </si>
+  <si>
+    <t>Risk Of Child Labour Incidents</t>
+  </si>
+  <si>
+    <t>RISK_OF_CHILD_LABOUR_INCIDENTS</t>
   </si>
   <si>
     <t>Operations or suppliers at significant risk of incidents of child labour.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 12</t>
   </si>
   <si>
+    <t>Risk Of Reported Forced Or Compulsory Labour Incidents</t>
+  </si>
+  <si>
+    <t>RISK_OF_REPORTED_FORCED_OR_COMPULSORY_LABOUR_INCIDENTS</t>
+  </si>
+  <si>
     <t>Operations or suppliers at significant risk of incidents of forced or compulsory labour.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 13</t>
   </si>
   <si>
-    <r>
-      <t>Number of cases of severe human rights issues and incidents connected to the company.</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 14</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Identified insufficiencies in actions taken to address breaches in procedures and standards of anti-corruption and anti-bribery.</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 16</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Number of reported convictions for violations of anti-corruption and anti-bribery laws.</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 17</t>
-    </r>
+    <t>Number Of Reported Incidents Of Human Rights Violations</t>
+  </si>
+  <si>
+    <t>NO_OF_REPORTED_INCIDENTS_OF_HUMAN_RIGHTS_VIOLATIONS</t>
+  </si>
+  <si>
+    <t>Number of cases of severe human rights issues and incidents connected to the company.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 14</t>
+  </si>
+  <si>
+    <t>Anti-corruption and anti-bribery</t>
+  </si>
+  <si>
+    <t>Cases of Insufficient Action against Bribery and Corruption</t>
+  </si>
+  <si>
+    <t>CASES_OF_INSUFFICIENT_ACTION_AGAINST_BRIBERY_AND_CORRUPTION</t>
+  </si>
+  <si>
+    <t>Identified insufficiencies in actions taken to address breaches in procedures and standards of anti-corruption and anti-bribery.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 16</t>
+  </si>
+  <si>
+    <t>Number Of Reported Convictions Of Bribery And Corruption</t>
+  </si>
+  <si>
+    <t>Number of reported convictions for violations of anti-corruption and anti-bribery laws.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 17</t>
+  </si>
+  <si>
+    <t>Total Amount Of Reported Fines Of Bribery and Corruption</t>
+  </si>
+  <si>
+    <t>TOTAL_AMOUNT_OF_REPORTED_FINES_OF_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
     <t>Amount of fines for violations of anti-corruption and anti-bribery laws.
 Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 17</t>
   </si>
   <si>
-    <t>Scope 3 downstream GHG emissions</t>
-  </si>
-  <si>
-    <t>Data Point Type Name Overwrite</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Water Consumption</t>
-    </r>
-  </si>
-  <si>
-    <t>Tons of scope 4 GHG emissions per million EUR revenue. As per the GHG Protocol, Scope 4 refers to emissions avoided when a product is used as a substitute for other goods or services, providing the same functions with a lower carbon footprint.</t>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>NUMBER_OF_REPORTED_CONVICTIONS_OF_BRIBERY_AND_CORRUPTION</t>
+  </si>
+  <si>
+    <t>PPP adjusted Gross Domestic Product (GDP)</t>
+  </si>
+  <si>
+    <t>PPP_ADJUSTED_GDP_IN_USD</t>
+  </si>
+  <si>
+    <t>A country’s total economic output, adjusted for differences in purchasing power (PPP) in US-dollar. See also PCAF (2025). The Global GHG Accounting and Reporting Standard Part A: Financed Emissions. Third Edition.</t>
+  </si>
+  <si>
+    <t>A country’s total economic output in euros. See also Regulation (EU) 2022/1288, Annex I, formula (4). Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 15</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1641,11 +1345,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
@@ -1671,13 +1370,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <strike/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1690,12 +1382,18 @@
       <name val="Roboto"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1710,17 +1408,17 @@
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -1729,18 +1427,53 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{F4874FAC-3F68-485B-89BC-5B693C7A2A35}"/>
-    <cellStyle name="Normal 3" xfId="2" xr:uid="{074E82A9-1A36-405D-A4C5-F2557832B1C3}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2052,10 +1785,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P114"/>
+  <dimension ref="A1:R111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="45.7109375" customWidth="1"/>
     <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="58.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="64.5703125" bestFit="1" customWidth="1"/>
@@ -2070,7 +1804,7 @@
     <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2117,500 +1851,571 @@
         <v>14</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="5" t="s">
         <v>16</v>
       </c>
+      <c r="D2" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="E2" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:18">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="4">
+    <row r="4" spans="1:18">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="B4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="E4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="10">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:16" s="6" customFormat="1">
-      <c r="A6" s="4">
+      <c r="I5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
+      <c r="B6" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="C6" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="E6" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" s="6" customFormat="1">
-      <c r="A7" s="4">
+      <c r="F6" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="10">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="B7" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="J7" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="10">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
+      <c r="K8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="10">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" s="6" customFormat="1">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4" t="s">
+      <c r="C9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" s="6" customFormat="1">
-      <c r="A9" s="4">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4" t="s">
+      <c r="E9" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" s="6" customFormat="1">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4" t="s">
+      <c r="C10" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="10">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" s="6" customFormat="1">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="C11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4" t="s">
+      <c r="D11" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+    </row>
+    <row r="12" spans="1:18" s="6" customFormat="1">
+      <c r="A12" s="10">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" s="6" customFormat="1">
-      <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4" t="s">
+      <c r="C12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+    </row>
+    <row r="13" spans="1:18" s="6" customFormat="1">
+      <c r="A13" s="10">
+        <v>12</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" s="6" customFormat="1">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4" t="s">
+      <c r="C13" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+    </row>
+    <row r="14" spans="1:18" s="6" customFormat="1">
+      <c r="A14" s="10">
+        <v>13</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" s="6" customFormat="1">
-      <c r="A14" s="4">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" s="6" customFormat="1">
+      <c r="C14" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+    </row>
+    <row r="15" spans="1:18" s="6" customFormat="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>388</v>
+        <v>69</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>297</v>
+        <v>71</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I15" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="J15" s="4" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="6" customFormat="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>298</v>
+        <v>76</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="6" customFormat="1">
@@ -2618,30 +2423,32 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>299</v>
+        <v>79</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I17" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="J17" s="4" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="6" customFormat="1">
@@ -2649,30 +2456,32 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I18" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="J18" s="4" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="6" customFormat="1">
@@ -2680,30 +2489,30 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="6" customFormat="1">
@@ -2711,30 +2520,30 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>301</v>
+        <v>88</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="6" customFormat="1">
@@ -2742,30 +2551,30 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>302</v>
+        <v>91</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="6" customFormat="1">
@@ -2773,30 +2582,32 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>303</v>
+        <v>94</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I22" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="J22" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="6" customFormat="1">
@@ -2804,30 +2615,30 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>304</v>
+        <v>97</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="6" customFormat="1">
@@ -2835,30 +2646,30 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>305</v>
+        <v>100</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="6" customFormat="1">
@@ -2866,30 +2677,30 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>306</v>
+        <v>103</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="6" customFormat="1">
@@ -2897,30 +2708,30 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>307</v>
+        <v>106</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="6" customFormat="1">
@@ -2928,30 +2739,30 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>391</v>
+        <v>109</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="6" customFormat="1">
@@ -2959,92 +2770,92 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="G28"/>
+        <v>112</v>
+      </c>
+      <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J28" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="K28" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="6" customFormat="1">
       <c r="A29" s="4">
         <v>28</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>34</v>
+      <c r="B29" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>309</v>
+        <v>116</v>
       </c>
       <c r="G29" s="4"/>
-      <c r="H29" s="5" t="s">
-        <v>38</v>
+      <c r="H29" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="I29" s="4"/>
-      <c r="J29" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>26</v>
+      <c r="J29" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="6" customFormat="1">
       <c r="A30" s="4">
         <v>29</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>34</v>
+      <c r="B30" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>310</v>
+        <v>120</v>
       </c>
       <c r="G30" s="4"/>
-      <c r="H30" s="5" t="s">
-        <v>38</v>
+      <c r="H30" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="I30" s="4"/>
-      <c r="J30" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>26</v>
+      <c r="J30" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="6" customFormat="1">
@@ -3052,32 +2863,30 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>311</v>
+        <v>123</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>39</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I31" s="4"/>
       <c r="J31" s="4" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="6" customFormat="1">
@@ -3085,32 +2894,30 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>312</v>
+        <v>126</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>39</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I32" s="4"/>
       <c r="J32" s="4" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="6" customFormat="1">
@@ -3118,98 +2925,91 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="G33" s="4"/>
+        <v>129</v>
+      </c>
       <c r="H33" s="4" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>98</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="J33" s="4"/>
       <c r="K33" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="6" customFormat="1">
       <c r="A34" s="4">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>34</v>
+      <c r="B34" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>314</v>
+        <v>133</v>
       </c>
       <c r="G34" s="4"/>
-      <c r="H34" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>26</v>
+      <c r="H34" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I34" s="4"/>
+      <c r="J34" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="6" customFormat="1">
       <c r="A35" s="4">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>34</v>
+      <c r="B35" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>315</v>
+        <v>137</v>
       </c>
       <c r="G35" s="4"/>
-      <c r="H35" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>26</v>
+      <c r="H35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I35" s="4"/>
+      <c r="J35" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="6" customFormat="1">
@@ -3217,32 +3017,32 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>316</v>
+        <v>141</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="6" customFormat="1">
@@ -3250,32 +3050,32 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="G37"/>
+        <v>145</v>
+      </c>
+      <c r="G37" s="4"/>
       <c r="H37" s="4" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="6" customFormat="1">
@@ -3283,32 +3083,32 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>318</v>
+        <v>148</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:11" s="6" customFormat="1">
@@ -3316,32 +3116,32 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>319</v>
+        <v>151</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="6" customFormat="1">
@@ -3349,32 +3149,32 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>320</v>
+        <v>155</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="6" customFormat="1">
@@ -3382,32 +3182,32 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>321</v>
+        <v>158</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="6" customFormat="1">
@@ -3415,32 +3215,32 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>322</v>
+        <v>161</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="6" customFormat="1">
@@ -3448,32 +3248,32 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>323</v>
+        <v>164</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="6" customFormat="1">
@@ -3481,32 +3281,32 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>324</v>
+        <v>167</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="6" customFormat="1">
@@ -3514,32 +3314,32 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>325</v>
+        <v>170</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="6" customFormat="1">
@@ -3547,32 +3347,32 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="G46"/>
+        <v>173</v>
+      </c>
+      <c r="G46" s="4"/>
       <c r="H46" s="4" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="6" customFormat="1">
@@ -3580,32 +3380,32 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="G47"/>
+        <v>176</v>
+      </c>
+      <c r="G47" s="4"/>
       <c r="H47" s="4" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="6" customFormat="1">
@@ -3613,32 +3413,32 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>328</v>
+        <v>179</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:11" s="6" customFormat="1">
@@ -3646,32 +3446,32 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="G49"/>
+        <v>182</v>
+      </c>
+      <c r="G49" s="4"/>
       <c r="H49" s="4" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="6" customFormat="1">
@@ -3679,32 +3479,31 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="G50"/>
+        <v>186</v>
+      </c>
       <c r="H50" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:11" s="6" customFormat="1">
@@ -3712,32 +3511,31 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="G51"/>
+        <v>189</v>
+      </c>
       <c r="H51" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="6" customFormat="1">
@@ -3745,32 +3543,32 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="G52"/>
+        <v>192</v>
+      </c>
+      <c r="G52" s="4"/>
       <c r="H52" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="6" customFormat="1">
@@ -3778,32 +3576,31 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>145</v>
+        <v>194</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="G53"/>
+        <v>195</v>
+      </c>
       <c r="H53" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:11" s="6" customFormat="1">
@@ -3811,32 +3608,31 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>146</v>
+        <v>196</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="G54"/>
+        <v>198</v>
+      </c>
       <c r="H54" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:11" s="6" customFormat="1">
@@ -3844,32 +3640,31 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>148</v>
+        <v>199</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>149</v>
+        <v>200</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="G55"/>
+        <v>201</v>
+      </c>
       <c r="H55" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:11" s="6" customFormat="1">
@@ -3877,32 +3672,31 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>150</v>
+        <v>202</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="G56"/>
+        <v>204</v>
+      </c>
       <c r="H56" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:11" s="6" customFormat="1">
@@ -3910,32 +3704,31 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>153</v>
+        <v>205</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="G57" s="4"/>
+        <v>207</v>
+      </c>
       <c r="H57" s="4" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:11" s="6" customFormat="1">
@@ -3943,32 +3736,31 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>390</v>
+        <v>208</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>155</v>
+        <v>209</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="G58" s="4"/>
+        <v>210</v>
+      </c>
       <c r="H58" s="4" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>156</v>
+        <v>17</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="6" customFormat="1">
@@ -3976,32 +3768,31 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>157</v>
+        <v>211</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>158</v>
+        <v>212</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="G59" s="4"/>
+        <v>213</v>
+      </c>
       <c r="H59" s="4" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>156</v>
+        <v>17</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:11" s="6" customFormat="1">
@@ -4009,32 +3800,32 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>340</v>
+        <v>217</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>161</v>
+        <v>42</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:11" s="6" customFormat="1">
@@ -4042,32 +3833,32 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>162</v>
+        <v>218</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>163</v>
+        <v>219</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="G61"/>
+        <v>220</v>
+      </c>
+      <c r="G61" s="4"/>
       <c r="H61" s="4" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>19</v>
+        <v>221</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="6" customFormat="1">
@@ -4075,32 +3866,32 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>164</v>
+        <v>222</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>165</v>
+        <v>223</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="G62"/>
+        <v>224</v>
+      </c>
+      <c r="G62" s="4"/>
       <c r="H62" s="4" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>19</v>
+        <v>221</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:11" s="6" customFormat="1">
@@ -4108,32 +3899,32 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>166</v>
+        <v>214</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>167</v>
+        <v>225</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>168</v>
+        <v>226</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>343</v>
+        <v>227</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>228</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:11" s="6" customFormat="1">
@@ -4141,32 +3932,31 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>166</v>
+        <v>214</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>169</v>
+        <v>229</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="G64" s="4"/>
+        <v>231</v>
+      </c>
       <c r="H64" s="4" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="6" customFormat="1">
@@ -4174,32 +3964,31 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>171</v>
+        <v>214</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>172</v>
+        <v>232</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>173</v>
+        <v>233</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="G65" s="4"/>
+        <v>234</v>
+      </c>
       <c r="H65" s="4" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:11" s="6" customFormat="1">
@@ -4207,32 +3996,32 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>171</v>
+        <v>235</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>174</v>
+        <v>236</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>346</v>
+        <v>238</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:11" s="6" customFormat="1">
@@ -4240,32 +4029,32 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>171</v>
+        <v>235</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>177</v>
+        <v>240</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>347</v>
+        <v>241</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="6" customFormat="1">
@@ -4273,32 +4062,32 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>171</v>
+        <v>242</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>178</v>
+        <v>243</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>179</v>
+        <v>244</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="G68"/>
+        <v>245</v>
+      </c>
+      <c r="G68" s="4"/>
       <c r="H68" s="4" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:11" s="6" customFormat="1">
@@ -4306,32 +4095,32 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>182</v>
+        <v>246</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>183</v>
+        <v>247</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="G69"/>
+        <v>248</v>
+      </c>
+      <c r="G69" s="4"/>
       <c r="H69" s="4" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="6" customFormat="1">
@@ -4339,32 +4128,32 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>184</v>
+        <v>249</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>185</v>
+        <v>250</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="G70"/>
+        <v>251</v>
+      </c>
+      <c r="G70" s="4"/>
       <c r="H70" s="4" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="6" customFormat="1">
@@ -4372,32 +4161,31 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>186</v>
+        <v>252</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>187</v>
+        <v>253</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G71"/>
+        <v>254</v>
+      </c>
       <c r="H71" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="6" customFormat="1">
@@ -4405,32 +4193,31 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="G72"/>
+        <v>259</v>
+      </c>
       <c r="H72" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:11" s="6" customFormat="1">
@@ -4438,32 +4225,31 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>192</v>
+        <v>261</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G73" s="5"/>
+        <v>262</v>
+      </c>
       <c r="H73" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:11" s="6" customFormat="1">
@@ -4471,32 +4257,31 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>194</v>
+        <v>263</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>195</v>
+        <v>264</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="G74" s="5"/>
+        <v>265</v>
+      </c>
       <c r="H74" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:11" s="6" customFormat="1">
@@ -4504,32 +4289,31 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>196</v>
+        <v>266</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="G75" s="5"/>
+        <v>268</v>
+      </c>
       <c r="H75" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:11" s="6" customFormat="1">
@@ -4537,32 +4321,32 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>198</v>
+        <v>269</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>199</v>
+        <v>270</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="G76" s="4"/>
+        <v>271</v>
+      </c>
+      <c r="G76" s="5"/>
       <c r="H76" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="6" customFormat="1">
@@ -4570,32 +4354,32 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>201</v>
+        <v>273</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G77" s="4"/>
+        <v>274</v>
+      </c>
+      <c r="G77" s="5"/>
       <c r="H77" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:11" s="6" customFormat="1">
@@ -4603,32 +4387,32 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>203</v>
+        <v>275</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>204</v>
+        <v>276</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="G78"/>
+        <v>277</v>
+      </c>
+      <c r="G78" s="4"/>
       <c r="H78" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:11" s="6" customFormat="1">
@@ -4636,32 +4420,32 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>205</v>
+        <v>278</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>206</v>
+        <v>279</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="G79"/>
+        <v>280</v>
+      </c>
+      <c r="G79" s="4"/>
       <c r="H79" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="6" customFormat="1">
@@ -4669,32 +4453,31 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>207</v>
+        <v>281</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>208</v>
+        <v>282</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G80" s="4"/>
+        <v>283</v>
+      </c>
       <c r="H80" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:11" s="6" customFormat="1">
@@ -4702,32 +4485,32 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>210</v>
+        <v>284</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>212</v>
+        <v>286</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:11" s="6" customFormat="1">
@@ -4735,32 +4518,32 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>213</v>
+        <v>287</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>214</v>
+        <v>288</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>215</v>
+        <v>289</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="6" customFormat="1">
@@ -4768,32 +4551,32 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>216</v>
+        <v>290</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>217</v>
+        <v>291</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>357</v>
+        <v>292</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="6" customFormat="1">
@@ -4801,32 +4584,31 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>218</v>
+        <v>293</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>219</v>
+        <v>294</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="G84"/>
+        <v>295</v>
+      </c>
       <c r="H84" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:11" s="6" customFormat="1">
@@ -4834,32 +4616,31 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>220</v>
+        <v>296</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>221</v>
+        <v>297</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="G85"/>
+        <v>298</v>
+      </c>
       <c r="H85" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="6" customFormat="1">
@@ -4867,32 +4648,30 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>222</v>
+        <v>299</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>223</v>
+        <v>300</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>360</v>
+        <v>301</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="I86" s="4" t="s">
-        <v>39</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I86" s="4"/>
       <c r="J86" s="4" t="s">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:11" s="6" customFormat="1">
@@ -4900,32 +4679,30 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>225</v>
+        <v>302</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>226</v>
+        <v>303</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>361</v>
+        <v>304</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4" t="s">
-        <v>224</v>
+        <v>305</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J87" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="J87" s="4"/>
       <c r="K87" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:11" s="6" customFormat="1">
@@ -4933,30 +4710,30 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>227</v>
+        <v>306</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>228</v>
+        <v>307</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>362</v>
+        <v>308</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I88" s="4"/>
-      <c r="J88" s="4" t="s">
-        <v>105</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J88" s="4"/>
       <c r="K88" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="6" customFormat="1">
@@ -4964,30 +4741,30 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>229</v>
+        <v>309</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>230</v>
+        <v>310</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>363</v>
+        <v>311</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
-        <v>231</v>
+        <v>305</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J89" s="4"/>
       <c r="K89" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:11" s="6" customFormat="1">
@@ -4995,30 +4772,30 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>232</v>
+        <v>312</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>233</v>
+        <v>313</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>364</v>
+        <v>314</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
-        <v>231</v>
+        <v>305</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J90" s="4"/>
       <c r="K90" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:11" s="6" customFormat="1">
@@ -5026,30 +4803,32 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>234</v>
+        <v>315</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>235</v>
+        <v>316</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>365</v>
+        <v>317</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4" t="s">
-        <v>231</v>
+        <v>41</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J91" s="4"/>
+        <v>318</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>152</v>
+      </c>
       <c r="K91" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="6" customFormat="1">
@@ -5057,30 +4836,32 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>236</v>
+        <v>319</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>237</v>
+        <v>320</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>366</v>
+        <v>321</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4" t="s">
-        <v>231</v>
+        <v>41</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J92" s="4"/>
+        <v>318</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>152</v>
+      </c>
       <c r="K92" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:11" s="6" customFormat="1">
@@ -5088,32 +4869,31 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>238</v>
+        <v>322</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="G93" s="4"/>
+        <v>324</v>
+      </c>
       <c r="H93" s="4" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>240</v>
+        <v>17</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="6" customFormat="1">
@@ -5121,32 +4901,31 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>241</v>
+        <v>325</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>242</v>
+        <v>326</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="G94" s="4"/>
+        <v>327</v>
+      </c>
       <c r="H94" s="4" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>240</v>
+        <v>17</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:11" s="6" customFormat="1">
@@ -5154,32 +4933,30 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>243</v>
+        <v>328</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>244</v>
+        <v>329</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="G95"/>
+        <v>330</v>
+      </c>
+      <c r="G95" s="4"/>
       <c r="H95" s="4" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J95" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="J95" s="4"/>
       <c r="K95" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:11" s="6" customFormat="1">
@@ -5187,626 +4964,529 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>245</v>
+        <v>331</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>246</v>
+        <v>332</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="G96"/>
+        <v>333</v>
+      </c>
+      <c r="G96" s="4"/>
       <c r="H96" s="4" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>19</v>
+        <v>334</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" s="6" customFormat="1">
       <c r="A97" s="4">
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>247</v>
+        <v>335</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>248</v>
+        <v>336</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="G97" s="4"/>
+        <v>337</v>
+      </c>
       <c r="H97" s="4" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J97" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="K97" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" s="6" customFormat="1">
       <c r="A98" s="4">
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>249</v>
+        <v>338</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>250</v>
+        <v>339</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="G98" s="4"/>
+        <v>340</v>
+      </c>
       <c r="H98" s="4" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>251</v>
+        <v>17</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" s="6" customFormat="1">
       <c r="A99" s="4">
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>252</v>
+        <v>341</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>253</v>
+        <v>342</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="G99"/>
+        <v>343</v>
+      </c>
       <c r="H99" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" s="6" customFormat="1">
       <c r="A100" s="4">
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>254</v>
+        <v>344</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>255</v>
+        <v>345</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="G100"/>
+        <v>346</v>
+      </c>
+      <c r="G100" s="4"/>
       <c r="H100" s="4" t="s">
-        <v>89</v>
+        <v>305</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" s="6" customFormat="1">
       <c r="A101" s="4">
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>256</v>
+        <v>347</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>257</v>
+        <v>348</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="G101"/>
+        <v>349</v>
+      </c>
+      <c r="G101" s="4"/>
       <c r="H101" s="4" t="s">
-        <v>89</v>
+        <v>305</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" s="6" customFormat="1">
       <c r="A102" s="4">
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>258</v>
+        <v>350</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>259</v>
+        <v>351</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
-        <v>231</v>
+        <v>41</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J102" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="J102" s="4"/>
       <c r="K102" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" s="6" customFormat="1">
       <c r="A103" s="4">
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>181</v>
+        <v>353</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>260</v>
+        <v>354</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>261</v>
+        <v>355</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="G103" s="4"/>
+        <v>356</v>
+      </c>
       <c r="H103" s="4" t="s">
-        <v>231</v>
+        <v>130</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" s="6" customFormat="1">
       <c r="A104" s="4">
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>181</v>
+        <v>353</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>262</v>
+        <v>357</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>263</v>
+        <v>358</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="G104" s="4"/>
+        <v>359</v>
+      </c>
       <c r="H104" s="4" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J104" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J104" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="K104" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" s="6" customFormat="1">
       <c r="A105" s="4">
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>264</v>
+        <v>353</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>265</v>
+        <v>360</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>266</v>
+        <v>361</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="G105" s="5"/>
+        <v>362</v>
+      </c>
       <c r="H105" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" s="6" customFormat="1">
       <c r="A106" s="4">
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>268</v>
+        <v>353</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>270</v>
+        <v>364</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="G106"/>
+        <v>365</v>
+      </c>
       <c r="H106" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" s="6" customFormat="1">
       <c r="A107" s="4">
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>268</v>
+        <v>353</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>272</v>
+        <v>366</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>367</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="G107"/>
+        <v>368</v>
+      </c>
       <c r="H107" s="4" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
       <c r="A108" s="4">
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>268</v>
+        <v>353</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>273</v>
+        <v>369</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>274</v>
+        <v>370</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="G108"/>
+        <v>371</v>
+      </c>
+      <c r="G108" s="4"/>
       <c r="H108" s="4" t="s">
-        <v>89</v>
+        <v>305</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
       <c r="A109" s="4">
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>268</v>
+        <v>372</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>275</v>
+        <v>373</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>276</v>
+        <v>374</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="G109"/>
+        <v>375</v>
+      </c>
+      <c r="G109" s="4"/>
       <c r="H109" s="4" t="s">
-        <v>89</v>
+        <v>305</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
       <c r="A110" s="4">
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>268</v>
+        <v>372</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>278</v>
+        <v>376</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>382</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="G110"/>
+        <v>377</v>
+      </c>
+      <c r="G110" s="4"/>
       <c r="H110" s="4" t="s">
-        <v>89</v>
+        <v>305</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" s="6" customFormat="1">
+        <v>20</v>
+      </c>
+      <c r="L110" s="6"/>
+      <c r="M110" s="6"/>
+      <c r="N110" s="6"/>
+      <c r="O110" s="6"/>
+    </row>
+    <row r="111" spans="1:15">
       <c r="A111" s="4">
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>268</v>
+        <v>372</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>279</v>
+        <v>378</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>280</v>
+        <v>379</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="s">
-        <v>231</v>
+        <v>381</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" s="6" customFormat="1">
-      <c r="A112" s="4">
-        <v>111</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D112" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="G112" s="4"/>
-      <c r="H112" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="I112" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J112" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K112" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" s="6" customFormat="1">
-      <c r="A113" s="4">
-        <v>112</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D113" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="G113" s="4"/>
-      <c r="H113" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="I113" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J113" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K113" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" s="6" customFormat="1">
-      <c r="A114" s="4">
-        <v>113</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D114" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="G114" s="4"/>
-      <c r="H114" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="I114" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J114" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K114" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="L111" s="6"/>
+      <c r="M111" s="6"/>
+      <c r="N111" s="6"/>
+      <c r="O111" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N114" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:N109" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
+++ b/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
@@ -148,13 +148,13 @@
     <t>MAIN_PCAF_SECTOR</t>
   </si>
   <si>
-    <t>One of the following sectors the company is mainly operating in: "Communication Services"; "Consumer Discretionary"; "Consumer Staples"; "Energy"; "Financials"; "Health Care"; "Industrials"; "Industry"; "Information Technology"; "Materials"; "Real estate"; "Sovereign"; "Utilities";</t>
+    <t>One of the following sectors the company is mainly operating in: "Communication Services"; "Consumer Discretionary"; "Consumer Staples"; "Energy"; "Financials"; "Health Care"; "Industrials"; "Information Technology"; "Materials"; "Public"; "Real estate"; "Utilities";</t>
   </si>
   <si>
     <t>Single-Select Dropdown</t>
   </si>
   <si>
-    <t>Communication Services|Consumer Discretionary|Consumer Staples|Energy|Financials|Health Care|Industrials|Industry|Information Technology|Materials|Real Estate|Sovereign|Utilities</t>
+    <t>Communication Services|Consumer Discretionary|Consumer Staples|Energy|Financials|Health Care|Industrials|Information Technology|Materials|Public|Real Estate|Utilities</t>
   </si>
   <si>
     <t>Company exchange status</t>

--- a/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
+++ b/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
@@ -133,7 +133,7 @@
     <t>Company</t>
   </si>
   <si>
-    <t>Fiscal Year End</t>
+    <t>Fiscal year end</t>
   </si>
   <si>
     <t>FISCAL_YEAR_END</t>
@@ -172,7 +172,7 @@
     <t>Financial</t>
   </si>
   <si>
-    <t>Gross Domestic Product (GDP)</t>
+    <t>Gross domestic product (GDP)</t>
   </si>
   <si>
     <t>GDP_IN_EUR</t>
@@ -227,7 +227,7 @@
     <t>Minorities interest in EUR as potentially listed on the balance sheet for ownerships without control (typically for ownerships of less than 50%)</t>
   </si>
   <si>
-    <t>Enterprise Value</t>
+    <t>Enterprise value</t>
   </si>
   <si>
     <t>ENTERPRISE_VALUE_IN_EUR</t>
@@ -1293,7 +1293,7 @@
     <t>NUMBER_OF_REPORTED_CONVICTIONS_OF_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
-    <t>PPP adjusted Gross Domestic Product (GDP)</t>
+    <t>PPP adjusted gross domestic product (GDP)</t>
   </si>
   <si>
     <t>PPP_ADJUSTED_GDP_IN_USD</t>
